--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:AE17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,6 +533,46 @@
       <c r="W1" t="inlineStr">
         <is>
           <t>e45_exposure</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>fuse_additive</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>dh_exposure_live</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>dh_id</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>dh_exposure</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>e16_financial_pre_dh</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>e16_telecom_pre_dh</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>e16_0050_pre_dh</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>live_cutover_ballot</t>
         </is>
       </c>
     </row>
@@ -602,6 +642,14 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -669,6 +717,14 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -736,6 +792,14 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -803,6 +867,14 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -870,6 +942,14 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -937,6 +1017,14 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1004,6 +1092,14 @@
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1071,6 +1167,14 @@
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1138,6 +1242,14 @@
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1205,6 +1317,14 @@
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1272,6 +1392,14 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1339,6 +1467,14 @@
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1416,6 +1552,14 @@
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1493,6 +1637,14 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1570,6 +1722,119 @@
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-09-14T15:10:22.390414+00:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.7366413617397212</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.1002546386571224</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-0.836896000396844</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.8742411434848937</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.0615768919647658</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.06418196455034041</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.8742411434827887</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.0615768919658533</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.064181964551358</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>FIN_PRE_EXDIV_KD</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>KD_APR15_MAY15_Klt30_T15</t>
+        </is>
+      </c>
+      <c r="T17" t="b">
+        <v>0</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>DH_dd06_vz1p0</t>
+        </is>
+      </c>
+      <c r="AA17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.8742411434848937</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.0615768919647658</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.06418196455034041</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: DH_dd06 + FUSE_ADDITIVE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1582,7 +1847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2374,6 +2639,54 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>557445522.172183</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1022.172182978364</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.8716272365175095</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.0589510520632536</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.0694198777473488</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.0104776600659046</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>E22_v2s_tw</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE17"/>
+  <dimension ref="A1:AE18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1836,6 +1836,111 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-09-15T08:54:56.504006+00:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6651345946942497</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.212353931525937</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-0.8774885262201868</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.8806808576136702</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.0661794982823404</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.0531396441039893</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.8806808576120915</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.066179498283156</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.0531396441047524</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>FIN_PRE_EXDIV_KD</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>KD_APR15_MAY15_Klt30_T15</t>
+        </is>
+      </c>
+      <c r="T18" t="b">
+        <v>0</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>DH_dd06_vz1p0</t>
+        </is>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.8806808576136702</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.0661794982823404</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.0531396441039893</v>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: DH_dd06 + FUSE_ADDITIVE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1847,7 +1952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2687,6 +2792,54 @@
         <v>0</v>
       </c>
       <c r="N17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>554725772.172183</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1022.172182978364</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.8707838615618995</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.0598782347355766</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.0693360610403756</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.0323946765349208</v>
+      </c>
+      <c r="H18" t="n">
+        <v>8</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="b">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>E22_v2s_tw</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2701,7 +2854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5022,6 +5175,214 @@
       </c>
       <c r="F89" t="n">
         <v>26.85</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-15-0050-SELL</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>50</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>63000</v>
+      </c>
+      <c r="F90" t="n">
+        <v>106.25</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-15-2412-BUY</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2412</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6000</v>
+      </c>
+      <c r="F91" t="n">
+        <v>143.5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-15-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>21000</v>
+      </c>
+      <c r="F92" t="n">
+        <v>46.9</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-15-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>19000</v>
+      </c>
+      <c r="F93" t="n">
+        <v>51.8</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-15-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>26000</v>
+      </c>
+      <c r="F94" t="n">
+        <v>39.55</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-15-3045-BUY</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>3045</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F95" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-15-4904-BUY</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F96" t="n">
+        <v>106.5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-15-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>38000</v>
+      </c>
+      <c r="F97" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE18"/>
+  <dimension ref="A1:AE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1941,6 +1941,111 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-09-16T09:19:22.965715+00:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7165214232611183</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.0642168652655862</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-0.7807382885267042</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.8806808576136702</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.0661794982823404</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.0531396441039893</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.8806808576120915</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.066179498283156</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.0531396441047524</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>FIN_PRE_EXDIV_KD</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>KD_APR15_MAY15_Klt30_T15</t>
+        </is>
+      </c>
+      <c r="T19" t="b">
+        <v>0</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>DH_dd06_vz1p0</t>
+        </is>
+      </c>
+      <c r="AA19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.8806808576136702</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.0661794982823404</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.0531396441039893</v>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: DH_dd06 + FUSE_ADDITIVE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1952,7 +2057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2840,6 +2945,54 @@
         <v>0</v>
       </c>
       <c r="N18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>556847465.5135857</v>
+      </c>
+      <c r="C19" t="n">
+        <v>50415.51358572836</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.8784334675005644</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.0640758954826014</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.0574000996314495</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.008611448440305</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>8</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>E22_v2s_tw_effex</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5396,7 +5549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J89"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8971,6 +9124,326 @@
         <v>5</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-09-15-0050-SELL</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>50</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>63000</v>
+      </c>
+      <c r="G90" t="n">
+        <v>106.096925</v>
+      </c>
+      <c r="H90" t="n">
+        <v>6684106.275</v>
+      </c>
+      <c r="I90" t="n">
+        <v>12399.017140125</v>
+      </c>
+      <c r="J90" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-09-15-2412-BUY</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>2412</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G91" t="n">
+        <v>143.57175</v>
+      </c>
+      <c r="H91" t="n">
+        <v>861430.4999999999</v>
+      </c>
+      <c r="I91" t="n">
+        <v>736.5230774999999</v>
+      </c>
+      <c r="J91" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-09-15-2880-BUY</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>21000</v>
+      </c>
+      <c r="G92" t="n">
+        <v>46.973475</v>
+      </c>
+      <c r="H92" t="n">
+        <v>986442.975</v>
+      </c>
+      <c r="I92" t="n">
+        <v>843.4087436249999</v>
+      </c>
+      <c r="J92" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-09-15-2886-BUY</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>19000</v>
+      </c>
+      <c r="G93" t="n">
+        <v>51.6258</v>
+      </c>
+      <c r="H93" t="n">
+        <v>980890.2</v>
+      </c>
+      <c r="I93" t="n">
+        <v>838.661121</v>
+      </c>
+      <c r="J93" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-09-15-2892-BUY</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>26000</v>
+      </c>
+      <c r="G94" t="n">
+        <v>39.71985</v>
+      </c>
+      <c r="H94" t="n">
+        <v>1032716.1</v>
+      </c>
+      <c r="I94" t="n">
+        <v>882.9722654999999</v>
+      </c>
+      <c r="J94" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-09-15-3045-BUY</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>3045</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>7000</v>
+      </c>
+      <c r="G95" t="n">
+        <v>124.062</v>
+      </c>
+      <c r="H95" t="n">
+        <v>868434</v>
+      </c>
+      <c r="I95" t="n">
+        <v>742.51107</v>
+      </c>
+      <c r="J95" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-09-15-4904-BUY</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G96" t="n">
+        <v>107.0535</v>
+      </c>
+      <c r="H96" t="n">
+        <v>856428</v>
+      </c>
+      <c r="I96" t="n">
+        <v>732.24594</v>
+      </c>
+      <c r="J96" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-09-15-5880-BUY</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>38000</v>
+      </c>
+      <c r="G97" t="n">
+        <v>27.11355</v>
+      </c>
+      <c r="H97" t="n">
+        <v>1030314.9</v>
+      </c>
+      <c r="I97" t="n">
+        <v>880.9192395</v>
+      </c>
+      <c r="J97" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE19"/>
+  <dimension ref="A1:AF20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,6 +573,11 @@
       <c r="AE1" t="inlineStr">
         <is>
           <t>live_cutover_ballot</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>e45_stitch_rollback</t>
         </is>
       </c>
     </row>
@@ -650,6 +655,7 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -725,6 +731,7 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -800,6 +807,7 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -875,6 +883,7 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -950,6 +959,7 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1025,6 +1035,7 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1100,6 +1111,7 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1175,6 +1187,7 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1250,6 +1263,7 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1325,6 +1339,7 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1400,6 +1415,7 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1475,6 +1491,7 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1560,6 +1577,7 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1645,6 +1663,7 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1730,6 +1749,7 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1835,6 +1855,7 @@
           <t>ACCEPT Live cutover: DH_dd06 + FUSE_ADDITIVE</t>
         </is>
       </c>
+      <c r="AF17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1940,6 +1961,7 @@
           <t>ACCEPT Live cutover: DH_dd06 + FUSE_ADDITIVE</t>
         </is>
       </c>
+      <c r="AF18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2043,6 +2065,117 @@
       <c r="AE19" t="inlineStr">
         <is>
           <t>ACCEPT Live cutover: DH_dd06 + FUSE_ADDITIVE</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:20:59.820566+00:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.5555474267120171</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.2321322128005977</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-0.3234152139114191</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.8806808576136702</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.0661794982823404</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.0531396441039893</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.8806808576120915</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.066179498283156</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.0531396441047524</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>FIN_PRE_EXDIV_KD</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>KD_APR15_MAY15_Klt30_T15</t>
+        </is>
+      </c>
+      <c r="T20" t="b">
+        <v>0</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>DH_dd06_vz1p0</t>
+        </is>
+      </c>
+      <c r="AA20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.8806808576136702</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.0661794982823404</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.0531396441039893</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: DH_dd06 + FUSE_ADDITIVE</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>ACCEPT_2026-09-09_DROP_E45_A05</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2131,6 +2264,21 @@
           <t>e22_stock_shares_added</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>e22_receivable_credit</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>e22_receivable_settled</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>e22_receivable_balance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2179,6 +2327,9 @@
       <c r="N2" t="n">
         <v>0</v>
       </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2227,6 +2378,9 @@
       <c r="N3" t="n">
         <v>0</v>
       </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2275,6 +2429,9 @@
       <c r="N4" t="n">
         <v>0</v>
       </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2323,6 +2480,9 @@
       <c r="N5" t="n">
         <v>0</v>
       </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2371,6 +2531,9 @@
       <c r="N6" t="n">
         <v>0</v>
       </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2419,6 +2582,9 @@
       <c r="N7" t="n">
         <v>0</v>
       </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2467,6 +2633,9 @@
       <c r="N8" t="n">
         <v>0</v>
       </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2515,6 +2684,9 @@
       <c r="N9" t="n">
         <v>0</v>
       </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2563,6 +2735,9 @@
       <c r="N10" t="n">
         <v>0</v>
       </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2611,6 +2786,9 @@
       <c r="N11" t="n">
         <v>0</v>
       </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2659,6 +2837,9 @@
       <c r="N12" t="n">
         <v>0</v>
       </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2707,6 +2888,9 @@
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2755,6 +2939,9 @@
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2803,6 +2990,9 @@
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2851,6 +3041,9 @@
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2899,6 +3092,9 @@
       <c r="N17" t="n">
         <v>0</v>
       </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2947,6 +3143,9 @@
       <c r="N18" t="n">
         <v>0</v>
       </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2993,6 +3192,66 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>555499915.5135857</v>
+      </c>
+      <c r="C20" t="n">
+        <v>50415.51358572836</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.8753941025362896</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.0645805678779129</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.05993457257184</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.0136806139496588</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="b">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>E22_v3_recv_pay_effdelay</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
         <v>0</v>
       </c>
     </row>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF20"/>
+  <dimension ref="A1:AF21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2179,6 +2179,116 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-09-22T13:35:15.620919+00:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0.546707502886276</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.269418626158842</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.277288876727434</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.8806808576136702</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.0661794982823404</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.0531396441039893</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.8806808576120915</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.066179498283156</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.0531396441047524</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>FIN_PRE_EXDIV_KD</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>KD_APR15_MAY15_Klt30_T15</t>
+        </is>
+      </c>
+      <c r="T21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>DH_dd06_vz1p0</t>
+        </is>
+      </c>
+      <c r="AA21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.8806808576136702</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.0661794982823404</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.0531396441039893</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: DH_dd06 + FUSE_ADDITIVE</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>ACCEPT_2026-09-09_DROP_E45_A05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2190,7 +2300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3252,6 +3362,63 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>553680015.5135857</v>
+      </c>
+      <c r="C21" t="n">
+        <v>50415.51358572836</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.8750007882271353</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.0645065723870679</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.060401584061109</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.014614935238927</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="b">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>E22_v3_recv_pay_effdelay</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
         <v>0</v>
       </c>
     </row>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF21"/>
+  <dimension ref="A1:AF22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2289,6 +2289,116 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-09-23T13:49:08.150570+00:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.5401752172526922</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.0984070451013149</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-0.4417681721513772</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.8806808576136702</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.0661794982823404</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.0531396441039893</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.8806808576120915</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.066179498283156</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.0531396441047524</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>FIN_PRE_EXDIV_KD</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>KD_APR15_MAY15_Klt30_T15</t>
+        </is>
+      </c>
+      <c r="T22" t="b">
+        <v>0</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>DH_dd06_vz1p0</t>
+        </is>
+      </c>
+      <c r="AA22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.8806808576136702</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0.0661794982823404</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.0531396441039893</v>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: DH_dd06 + FUSE_ADDITIVE</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>ACCEPT_2026-09-09_DROP_E45_A05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2300,7 +2410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3419,6 +3529,63 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>549283465.5135857</v>
+      </c>
+      <c r="C22" t="n">
+        <v>50415.51358572836</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.8735972045896794</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.06509935624325749</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.0612116550214424</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0162358059805268</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="b">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>E22_v3_recv_pay_effdelay</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
         <v>0</v>
       </c>
     </row>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF22"/>
+  <dimension ref="A1:AF23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2399,6 +2399,116 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-09-24T13:43:31.846651+00:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.5311834198087968</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-0.07947451338478689</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.4517089064240099</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.8806808576136702</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.0661794982823404</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.0531396441039893</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8806808576120915</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.066179498283156</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.0531396441047524</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>FIN_PRE_EXDIV_KD</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>KD_APR15_MAY15_Klt30_T15</t>
+        </is>
+      </c>
+      <c r="T23" t="b">
+        <v>0</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="b">
+        <v>1</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>DH_dd06_vz1p0</t>
+        </is>
+      </c>
+      <c r="AA23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.8806808576136702</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0.0661794982823404</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.0531396441039893</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: DH_dd06 + FUSE_ADDITIVE</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>ACCEPT_2026-09-09_DROP_E45_A05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2410,7 +2520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:Q23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3586,6 +3696,63 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>545727265.5135857</v>
+      </c>
+      <c r="C23" t="n">
+        <v>50415.51358572836</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.8729667365101444</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.0653577386616979</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.0615831425764878</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0169793791966667</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="b">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>E22_v3_recv_pay_effdelay</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>0</v>
       </c>
     </row>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF23"/>
+  <dimension ref="A1:BP24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,6 +578,186 @@
       <c r="AF1" t="inlineStr">
         <is>
           <t>e45_stitch_rollback</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>cool_exposure_live</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>cool_id</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>cool_exposure</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>e16_financial_pre_cool</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>e16_telecom_pre_cool</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>e16_0050_pre_cool</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>fin_priv_v7_f05_live</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>fin_priv_ballot</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>fin_priv_gate_on</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>fin_priv_frac</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>fin_priv_skipped_missing_px</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>conf_ret3_631l_live</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>conf_ret3_ballot</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>conf_ret3_off_weight</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>conf_ret3_pulse_active</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>conf_ret3_n_orders</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>path3_t0_emit_live</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>path3_t0_emit_ballot</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>path3_t0_emit_reason</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>path3_t0_n_orders</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>path3_t0_weight_engine_mode</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>path3_t0_weight_engine_ballot</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>path3_t0_weight_engine_id</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>path3_t0_weight_reason</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>path3_t0_weight_n_delta_names</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>soft_path3_coexist_mute_live</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>soft_path3_coexist_mute_ballot</t>
+        </is>
+      </c>
+      <c r="BH1" t="inlineStr">
+        <is>
+          <t>soft_path3_coexist_mute_policy</t>
+        </is>
+      </c>
+      <c r="BI1" t="inlineStr">
+        <is>
+          <t>soft_path3_coexist_mute_applied</t>
+        </is>
+      </c>
+      <c r="BJ1" t="inlineStr">
+        <is>
+          <t>soft_path3_coexist_mute_n_muted</t>
+        </is>
+      </c>
+      <c r="BK1" t="inlineStr">
+        <is>
+          <t>tel_t3_cool_inv_vol20_live</t>
+        </is>
+      </c>
+      <c r="BL1" t="inlineStr">
+        <is>
+          <t>tel_t3_ballot</t>
+        </is>
+      </c>
+      <c r="BM1" t="inlineStr">
+        <is>
+          <t>telecom_alloc</t>
+        </is>
+      </c>
+      <c r="BN1" t="inlineStr">
+        <is>
+          <t>tel_t3_active</t>
+        </is>
+      </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>tel_t3_defending</t>
+        </is>
+      </c>
+      <c r="BP1" t="inlineStr">
+        <is>
+          <t>tel_t3_recipe</t>
         </is>
       </c>
     </row>
@@ -656,6 +836,42 @@
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
+      <c r="BP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -732,6 +948,42 @@
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -808,6 +1060,42 @@
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -884,6 +1172,42 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -960,6 +1284,42 @@
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1036,6 +1396,42 @@
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1112,6 +1508,42 @@
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1188,6 +1620,42 @@
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1264,6 +1732,42 @@
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1340,6 +1844,42 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr"/>
       <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+      <c r="BO11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1416,6 +1956,42 @@
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr"/>
       <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1492,6 +2068,42 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr"/>
       <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1578,6 +2190,42 @@
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr"/>
       <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1664,6 +2312,42 @@
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr"/>
       <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+      <c r="BO15" t="inlineStr"/>
+      <c r="BP15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1750,6 +2434,42 @@
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr"/>
       <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+      <c r="BO16" t="inlineStr"/>
+      <c r="BP16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1856,6 +2576,42 @@
         </is>
       </c>
       <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
+      <c r="BO17" t="inlineStr"/>
+      <c r="BP17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1962,6 +2718,42 @@
         </is>
       </c>
       <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="inlineStr"/>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="inlineStr"/>
+      <c r="BC18" t="inlineStr"/>
+      <c r="BD18" t="inlineStr"/>
+      <c r="BE18" t="inlineStr"/>
+      <c r="BF18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr"/>
+      <c r="BH18" t="inlineStr"/>
+      <c r="BI18" t="inlineStr"/>
+      <c r="BJ18" t="inlineStr"/>
+      <c r="BK18" t="inlineStr"/>
+      <c r="BL18" t="inlineStr"/>
+      <c r="BM18" t="inlineStr"/>
+      <c r="BN18" t="inlineStr"/>
+      <c r="BO18" t="inlineStr"/>
+      <c r="BP18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2068,6 +2860,42 @@
         </is>
       </c>
       <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="inlineStr"/>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="inlineStr"/>
+      <c r="BC19" t="inlineStr"/>
+      <c r="BD19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr"/>
+      <c r="BF19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr"/>
+      <c r="BH19" t="inlineStr"/>
+      <c r="BI19" t="inlineStr"/>
+      <c r="BJ19" t="inlineStr"/>
+      <c r="BK19" t="inlineStr"/>
+      <c r="BL19" t="inlineStr"/>
+      <c r="BM19" t="inlineStr"/>
+      <c r="BN19" t="inlineStr"/>
+      <c r="BO19" t="inlineStr"/>
+      <c r="BP19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2178,6 +3006,42 @@
           <t>ACCEPT_2026-09-09_DROP_E45_A05</t>
         </is>
       </c>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+      <c r="BK20" t="inlineStr"/>
+      <c r="BL20" t="inlineStr"/>
+      <c r="BM20" t="inlineStr"/>
+      <c r="BN20" t="inlineStr"/>
+      <c r="BO20" t="inlineStr"/>
+      <c r="BP20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2288,6 +3152,42 @@
           <t>ACCEPT_2026-09-09_DROP_E45_A05</t>
         </is>
       </c>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+      <c r="BK21" t="inlineStr"/>
+      <c r="BL21" t="inlineStr"/>
+      <c r="BM21" t="inlineStr"/>
+      <c r="BN21" t="inlineStr"/>
+      <c r="BO21" t="inlineStr"/>
+      <c r="BP21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2398,6 +3298,42 @@
           <t>ACCEPT_2026-09-09_DROP_E45_A05</t>
         </is>
       </c>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+      <c r="BK22" t="inlineStr"/>
+      <c r="BL22" t="inlineStr"/>
+      <c r="BM22" t="inlineStr"/>
+      <c r="BN22" t="inlineStr"/>
+      <c r="BO22" t="inlineStr"/>
+      <c r="BP22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2506,6 +3442,270 @@
       <c r="AF23" t="inlineStr">
         <is>
           <t>ACCEPT_2026-09-09_DROP_E45_A05</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr"/>
+      <c r="AH23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr"/>
+      <c r="AK23" t="inlineStr"/>
+      <c r="AL23" t="inlineStr"/>
+      <c r="AM23" t="inlineStr"/>
+      <c r="AN23" t="inlineStr"/>
+      <c r="AO23" t="inlineStr"/>
+      <c r="AP23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr"/>
+      <c r="AR23" t="inlineStr"/>
+      <c r="AS23" t="inlineStr"/>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AU23" t="inlineStr"/>
+      <c r="AV23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr"/>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr"/>
+      <c r="BA23" t="inlineStr"/>
+      <c r="BB23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr"/>
+      <c r="BD23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr"/>
+      <c r="BF23" t="inlineStr"/>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
+      <c r="BI23" t="inlineStr"/>
+      <c r="BJ23" t="inlineStr"/>
+      <c r="BK23" t="inlineStr"/>
+      <c r="BL23" t="inlineStr"/>
+      <c r="BM23" t="inlineStr"/>
+      <c r="BN23" t="inlineStr"/>
+      <c r="BO23" t="inlineStr"/>
+      <c r="BP23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-09-29T15:00:25.868062+00:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>0.5212029921015261</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.0476643099057838</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-0.5688673020073101</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.7549897760494932</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.1526640167411745</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.09234620720933211</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.7549897760493324</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.1526640167413354</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.0923462072093322</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>FIN_DUAL_PUB_PRIV</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>KD_APR15_MAY15_Klt30_T15</t>
+        </is>
+      </c>
+      <c r="T24" t="b">
+        <v>0</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: COOL_c8_f50_d21 (replace DH, keep FUSE)</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>ACCEPT_2026-09-09_DROP_E45_A05</t>
+        </is>
+      </c>
+      <c r="AG24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>COOL_c8_f50_d21</t>
+        </is>
+      </c>
+      <c r="AI24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.7549897760494932</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0.1526640167411745</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0.09234620720933211</v>
+      </c>
+      <c r="AM24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>ACCEPT Class D: FinPriv V7 F05</t>
+        </is>
+      </c>
+      <c r="AO24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AQ24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: CONF_RET3_A10_H5 (00631L short-assist under COOL)</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>ACCEPT Live Path3 switch emitter: T0_CARVE_FIN_SAT_SWITCH tagged orders (P3_T0_STATE · Soft-Frozen Exact T+1 KEEP elsewhere · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>no_flip</t>
+        </is>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>ledger</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>ACCEPT Path3 weight engine: P3_COMP_SAT_DAILY_POS_LEDGER_A (ledger-scaled recon · Soft 0050 KEEP · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr"/>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>no_flip</t>
+        </is>
+      </c>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="b">
+        <v>1</v>
+      </c>
+      <c r="BG24" t="inlineStr">
+        <is>
+          <t>ACCEPT Soft↔Path3 coexist mute: MUTE_SOFT_FIN_TEL (flip-day Soft FIN/TEL Exact T+1 muted · Soft 0050 KEEP · Path3 -P3T0 KEEP · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>MUTE_SOFT_FIN_TEL</t>
+        </is>
+      </c>
+      <c r="BI24" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK24" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL24" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: T3_COOL_INV_VOL20 (TEL within-sleeve under COOL)</t>
+        </is>
+      </c>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>TEL_EQUAL</t>
+        </is>
+      </c>
+      <c r="BN24" t="b">
+        <v>0</v>
+      </c>
+      <c r="BO24" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP24" t="inlineStr">
+        <is>
+          <t>LIVE_TEL_T3_COOL_INV_VOL20</t>
         </is>
       </c>
     </row>
@@ -2520,7 +3720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2609,6 +3809,16 @@
           <t>e22_receivable_balance</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>pre_00631l</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>conf_ret3_off_weight</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2660,6 +3870,8 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2711,6 +3923,8 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2762,6 +3976,8 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2813,6 +4029,8 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2864,6 +4082,8 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2915,6 +4135,8 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2966,6 +4188,8 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3017,6 +4241,8 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3068,6 +4294,8 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3119,6 +4347,8 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3170,6 +4400,8 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3221,6 +4453,8 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3272,6 +4506,8 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3323,6 +4559,8 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3374,6 +4612,8 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3425,6 +4665,8 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3476,6 +4718,8 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3527,6 +4771,8 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3584,6 +4830,8 @@
       <c r="Q20" t="n">
         <v>0</v>
       </c>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3641,6 +4889,8 @@
       <c r="Q21" t="n">
         <v>0</v>
       </c>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3698,6 +4948,8 @@
       <c r="Q22" t="n">
         <v>0</v>
       </c>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3753,6 +5005,71 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="inlineStr"/>
+      <c r="S23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>537036865.5135857</v>
+      </c>
+      <c r="C24" t="n">
+        <v>50415.51358572836</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.8721556751082131</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.0657831934241882</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.0619672542743867</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.2344256753106516</v>
+      </c>
+      <c r="H24" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="b">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>E22_v3_recv_pay_effdelay</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3767,7 +5084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6296,6 +7613,162 @@
       </c>
       <c r="F97" t="n">
         <v>27</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-29-2880-SELL</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>2880</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>249000</v>
+      </c>
+      <c r="F98" t="n">
+        <v>44.9</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-29-2886-SELL</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>2886</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>228000</v>
+      </c>
+      <c r="F99" t="n">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-29-2892-SELL</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>2892</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>290000</v>
+      </c>
+      <c r="F100" t="n">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-29-5880-SELL</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>5880</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>430000</v>
+      </c>
+      <c r="F101" t="n">
+        <v>26.05</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-29-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>50</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>109000</v>
+      </c>
+      <c r="F102" t="n">
+        <v>111.3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-29-4904-BUY</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>4904</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>111000</v>
+      </c>
+      <c r="F103" t="n">
+        <v>104.5</v>
       </c>
     </row>
   </sheetData>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP24"/>
+  <dimension ref="A1:BV25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -758,6 +758,36 @@
       <c r="BP1" t="inlineStr">
         <is>
           <t>tel_t3_recipe</t>
+        </is>
+      </c>
+      <c r="BQ1" t="inlineStr">
+        <is>
+          <t>soft_path3_coexist_mute_superseded_by_cutover</t>
+        </is>
+      </c>
+      <c r="BR1" t="inlineStr">
+        <is>
+          <t>path3_strategy_cutover_live</t>
+        </is>
+      </c>
+      <c r="BS1" t="inlineStr">
+        <is>
+          <t>path3_strategy_cutover_scope</t>
+        </is>
+      </c>
+      <c r="BT1" t="inlineStr">
+        <is>
+          <t>path3_strategy_cutover_ballot</t>
+        </is>
+      </c>
+      <c r="BU1" t="inlineStr">
+        <is>
+          <t>path3_strategy_cutover_applied</t>
+        </is>
+      </c>
+      <c r="BV1" t="inlineStr">
+        <is>
+          <t>path3_strategy_cutover_n_muted</t>
         </is>
       </c>
     </row>
@@ -872,6 +902,12 @@
       <c r="BN2" t="inlineStr"/>
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr"/>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -984,6 +1020,12 @@
       <c r="BN3" t="inlineStr"/>
       <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1096,6 +1138,12 @@
       <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1208,6 +1256,12 @@
       <c r="BN5" t="inlineStr"/>
       <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1320,6 +1374,12 @@
       <c r="BN6" t="inlineStr"/>
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1432,6 +1492,12 @@
       <c r="BN7" t="inlineStr"/>
       <c r="BO7" t="inlineStr"/>
       <c r="BP7" t="inlineStr"/>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1544,6 +1610,12 @@
       <c r="BN8" t="inlineStr"/>
       <c r="BO8" t="inlineStr"/>
       <c r="BP8" t="inlineStr"/>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1656,6 +1728,12 @@
       <c r="BN9" t="inlineStr"/>
       <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1768,6 +1846,12 @@
       <c r="BN10" t="inlineStr"/>
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1880,6 +1964,12 @@
       <c r="BN11" t="inlineStr"/>
       <c r="BO11" t="inlineStr"/>
       <c r="BP11" t="inlineStr"/>
+      <c r="BQ11" t="inlineStr"/>
+      <c r="BR11" t="inlineStr"/>
+      <c r="BS11" t="inlineStr"/>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1992,6 +2082,12 @@
       <c r="BN12" t="inlineStr"/>
       <c r="BO12" t="inlineStr"/>
       <c r="BP12" t="inlineStr"/>
+      <c r="BQ12" t="inlineStr"/>
+      <c r="BR12" t="inlineStr"/>
+      <c r="BS12" t="inlineStr"/>
+      <c r="BT12" t="inlineStr"/>
+      <c r="BU12" t="inlineStr"/>
+      <c r="BV12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2104,6 +2200,12 @@
       <c r="BN13" t="inlineStr"/>
       <c r="BO13" t="inlineStr"/>
       <c r="BP13" t="inlineStr"/>
+      <c r="BQ13" t="inlineStr"/>
+      <c r="BR13" t="inlineStr"/>
+      <c r="BS13" t="inlineStr"/>
+      <c r="BT13" t="inlineStr"/>
+      <c r="BU13" t="inlineStr"/>
+      <c r="BV13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2226,6 +2328,12 @@
       <c r="BN14" t="inlineStr"/>
       <c r="BO14" t="inlineStr"/>
       <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="inlineStr"/>
+      <c r="BR14" t="inlineStr"/>
+      <c r="BS14" t="inlineStr"/>
+      <c r="BT14" t="inlineStr"/>
+      <c r="BU14" t="inlineStr"/>
+      <c r="BV14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2348,6 +2456,12 @@
       <c r="BN15" t="inlineStr"/>
       <c r="BO15" t="inlineStr"/>
       <c r="BP15" t="inlineStr"/>
+      <c r="BQ15" t="inlineStr"/>
+      <c r="BR15" t="inlineStr"/>
+      <c r="BS15" t="inlineStr"/>
+      <c r="BT15" t="inlineStr"/>
+      <c r="BU15" t="inlineStr"/>
+      <c r="BV15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2470,6 +2584,12 @@
       <c r="BN16" t="inlineStr"/>
       <c r="BO16" t="inlineStr"/>
       <c r="BP16" t="inlineStr"/>
+      <c r="BQ16" t="inlineStr"/>
+      <c r="BR16" t="inlineStr"/>
+      <c r="BS16" t="inlineStr"/>
+      <c r="BT16" t="inlineStr"/>
+      <c r="BU16" t="inlineStr"/>
+      <c r="BV16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2612,6 +2732,12 @@
       <c r="BN17" t="inlineStr"/>
       <c r="BO17" t="inlineStr"/>
       <c r="BP17" t="inlineStr"/>
+      <c r="BQ17" t="inlineStr"/>
+      <c r="BR17" t="inlineStr"/>
+      <c r="BS17" t="inlineStr"/>
+      <c r="BT17" t="inlineStr"/>
+      <c r="BU17" t="inlineStr"/>
+      <c r="BV17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2754,6 +2880,12 @@
       <c r="BN18" t="inlineStr"/>
       <c r="BO18" t="inlineStr"/>
       <c r="BP18" t="inlineStr"/>
+      <c r="BQ18" t="inlineStr"/>
+      <c r="BR18" t="inlineStr"/>
+      <c r="BS18" t="inlineStr"/>
+      <c r="BT18" t="inlineStr"/>
+      <c r="BU18" t="inlineStr"/>
+      <c r="BV18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2896,6 +3028,12 @@
       <c r="BN19" t="inlineStr"/>
       <c r="BO19" t="inlineStr"/>
       <c r="BP19" t="inlineStr"/>
+      <c r="BQ19" t="inlineStr"/>
+      <c r="BR19" t="inlineStr"/>
+      <c r="BS19" t="inlineStr"/>
+      <c r="BT19" t="inlineStr"/>
+      <c r="BU19" t="inlineStr"/>
+      <c r="BV19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3042,6 +3180,12 @@
       <c r="BN20" t="inlineStr"/>
       <c r="BO20" t="inlineStr"/>
       <c r="BP20" t="inlineStr"/>
+      <c r="BQ20" t="inlineStr"/>
+      <c r="BR20" t="inlineStr"/>
+      <c r="BS20" t="inlineStr"/>
+      <c r="BT20" t="inlineStr"/>
+      <c r="BU20" t="inlineStr"/>
+      <c r="BV20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3188,6 +3332,12 @@
       <c r="BN21" t="inlineStr"/>
       <c r="BO21" t="inlineStr"/>
       <c r="BP21" t="inlineStr"/>
+      <c r="BQ21" t="inlineStr"/>
+      <c r="BR21" t="inlineStr"/>
+      <c r="BS21" t="inlineStr"/>
+      <c r="BT21" t="inlineStr"/>
+      <c r="BU21" t="inlineStr"/>
+      <c r="BV21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3334,6 +3484,12 @@
       <c r="BN22" t="inlineStr"/>
       <c r="BO22" t="inlineStr"/>
       <c r="BP22" t="inlineStr"/>
+      <c r="BQ22" t="inlineStr"/>
+      <c r="BR22" t="inlineStr"/>
+      <c r="BS22" t="inlineStr"/>
+      <c r="BT22" t="inlineStr"/>
+      <c r="BU22" t="inlineStr"/>
+      <c r="BV22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3480,6 +3636,12 @@
       <c r="BN23" t="inlineStr"/>
       <c r="BO23" t="inlineStr"/>
       <c r="BP23" t="inlineStr"/>
+      <c r="BQ23" t="inlineStr"/>
+      <c r="BR23" t="inlineStr"/>
+      <c r="BS23" t="inlineStr"/>
+      <c r="BT23" t="inlineStr"/>
+      <c r="BU23" t="inlineStr"/>
+      <c r="BV23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3707,6 +3869,268 @@
         <is>
           <t>LIVE_TEL_T3_COOL_INV_VOL20</t>
         </is>
+      </c>
+      <c r="BQ24" t="inlineStr"/>
+      <c r="BR24" t="inlineStr"/>
+      <c r="BS24" t="inlineStr"/>
+      <c r="BT24" t="inlineStr"/>
+      <c r="BU24" t="inlineStr"/>
+      <c r="BV24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-09-30T15:06:01.917129+00:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>0.3597386979054607</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.4956992568438784</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.135960558938418</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="n">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.7549897760494932</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.1526308129970603</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.0923794109534464</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.7549897760493323</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.1526308129972212</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.0923794109534464</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>FIN_DUAL_PUB_PRIV</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>KD_APR15_MAY15_Klt30_T15</t>
+        </is>
+      </c>
+      <c r="T25" t="b">
+        <v>0</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: COOL_c8_f50_d21 (replace DH, keep FUSE)</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>ACCEPT_2026-09-09_DROP_E45_A05</t>
+        </is>
+      </c>
+      <c r="AG25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>COOL_c8_f50_d21</t>
+        </is>
+      </c>
+      <c r="AI25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0.7549897760494932</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0.1526308129970603</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0.0923794109534464</v>
+      </c>
+      <c r="AM25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>ACCEPT Class D: FinPriv V7 F05</t>
+        </is>
+      </c>
+      <c r="AO25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AQ25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: CONF_RET3_A10_H5 (00631L short-assist under COOL)</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>ACCEPT Live Path3 switch emitter: T0_CARVE_FIN_SAT_SWITCH tagged orders (P3_T0_STATE · Soft-Frozen Exact T+1 KEEP elsewhere · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>weight_engine_not_wired</t>
+        </is>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>ledger</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>ACCEPT Path3 weight engine: P3_COMP_SAT_DAILY_POS_LEDGER_A (ledger-scaled recon · Soft 0050 KEEP · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>P3_COMP_SAT_DAILY_POS_LEDGER_A</t>
+        </is>
+      </c>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>ledger_stale</t>
+        </is>
+      </c>
+      <c r="BE25" t="inlineStr"/>
+      <c r="BF25" t="b">
+        <v>1</v>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>ACCEPT Soft↔Path3 coexist mute: MUTE_SOFT_FIN_TEL (flip-day Soft FIN/TEL Exact T+1 muted · Soft 0050 KEEP · Path3 -P3T0 KEEP · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>MUTE_SOFT_FIN_TEL</t>
+        </is>
+      </c>
+      <c r="BI25" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK25" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL25" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: T3_COOL_INV_VOL20 (TEL within-sleeve under COOL)</t>
+        </is>
+      </c>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>TEL_EQUAL</t>
+        </is>
+      </c>
+      <c r="BN25" t="b">
+        <v>0</v>
+      </c>
+      <c r="BO25" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP25" t="inlineStr">
+        <is>
+          <t>LIVE_TEL_T3_COOL_INV_VOL20</t>
+        </is>
+      </c>
+      <c r="BQ25" t="b">
+        <v>1</v>
+      </c>
+      <c r="BR25" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS25" t="inlineStr">
+        <is>
+          <t>WITHIN_SLEEVE_PATH3</t>
+        </is>
+      </c>
+      <c r="BT25" t="inlineStr">
+        <is>
+          <t>ACCEPT Path3 strategy cutover: WITHIN_SLEEVE_PATH3
+(Soft clips+0050 Exact T+1 KEEP · Soft FIN/TEL Exact T+1 OFF · Path3 ledger daily ·
+ T0_CARVE_FIN_SAT_SWITCH KEEP · broker false · overlays KEEP)</t>
+        </is>
+      </c>
+      <c r="BU25" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV25" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3720,7 +4144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S24"/>
+  <dimension ref="A1:S25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5070,6 +5494,69 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>538703968.8304424</v>
+      </c>
+      <c r="C25" t="n">
+        <v>21314018.83044248</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.7892174080748564</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.0863535498002649</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.0848636777249905</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.1080206284506144</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>E22_v3_recv_pay_effdelay</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5084,7 +5571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7769,6 +8256,32 @@
       </c>
       <c r="F103" t="n">
         <v>104.5</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-30-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>50</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>27000</v>
+      </c>
+      <c r="F104" t="n">
+        <v>112.05</v>
       </c>
     </row>
   </sheetData>
@@ -7782,7 +8295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J97"/>
+  <dimension ref="A1:J103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11677,6 +12190,246 @@
         <v>5</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-09-29-2880-SELL</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>2880</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>249000</v>
+      </c>
+      <c r="G98" t="n">
+        <v>45.67715</v>
+      </c>
+      <c r="H98" t="n">
+        <v>11373610.35</v>
+      </c>
+      <c r="I98" t="n">
+        <v>43845.26789925001</v>
+      </c>
+      <c r="J98" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-09-29-2886-SELL</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>2886</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>228000</v>
+      </c>
+      <c r="G99" t="n">
+        <v>49.525225</v>
+      </c>
+      <c r="H99" t="n">
+        <v>11291751.3</v>
+      </c>
+      <c r="I99" t="n">
+        <v>43529.7012615</v>
+      </c>
+      <c r="J99" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-09-29-2892-SELL</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>2892</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>290000</v>
+      </c>
+      <c r="G100" t="n">
+        <v>39.230375</v>
+      </c>
+      <c r="H100" t="n">
+        <v>11376808.75</v>
+      </c>
+      <c r="I100" t="n">
+        <v>43857.59773125</v>
+      </c>
+      <c r="J100" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-09-29-5880-SELL</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>5880</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>430000</v>
+      </c>
+      <c r="G101" t="n">
+        <v>26.3868</v>
+      </c>
+      <c r="H101" t="n">
+        <v>11346324</v>
+      </c>
+      <c r="I101" t="n">
+        <v>43740.07902</v>
+      </c>
+      <c r="J101" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-09-29-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>50</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>109000</v>
+      </c>
+      <c r="G102" t="n">
+        <v>112.55625</v>
+      </c>
+      <c r="H102" t="n">
+        <v>12268631.25</v>
+      </c>
+      <c r="I102" t="n">
+        <v>10489.67971875</v>
+      </c>
+      <c r="J102" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-09-29-4904-BUY</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>4904</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>111000</v>
+      </c>
+      <c r="G103" t="n">
+        <v>105.0525</v>
+      </c>
+      <c r="H103" t="n">
+        <v>11660827.5</v>
+      </c>
+      <c r="I103" t="n">
+        <v>9970.0075125</v>
+      </c>
+      <c r="J103" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV25"/>
+  <dimension ref="A1:CN26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,6 +788,96 @@
       <c r="BV1" t="inlineStr">
         <is>
           <t>path3_strategy_cutover_n_muted</t>
+        </is>
+      </c>
+      <c r="BW1" t="inlineStr">
+        <is>
+          <t>tipsoft_live_override_live</t>
+        </is>
+      </c>
+      <c r="BX1" t="inlineStr">
+        <is>
+          <t>tipsoft_live_override_wire_mode</t>
+        </is>
+      </c>
+      <c r="BY1" t="inlineStr">
+        <is>
+          <t>tipsoft_live_override_policy</t>
+        </is>
+      </c>
+      <c r="BZ1" t="inlineStr">
+        <is>
+          <t>tipsoft_live_override_stage_a_arm</t>
+        </is>
+      </c>
+      <c r="CA1" t="inlineStr">
+        <is>
+          <t>tipsoft_live_override_ballot</t>
+        </is>
+      </c>
+      <c r="CB1" t="inlineStr">
+        <is>
+          <t>tipsoft_live_override_cutover</t>
+        </is>
+      </c>
+      <c r="CC1" t="inlineStr">
+        <is>
+          <t>tipsoft_live_override_rollback</t>
+        </is>
+      </c>
+      <c r="CD1" t="inlineStr">
+        <is>
+          <t>tipsoft_override_on</t>
+        </is>
+      </c>
+      <c r="CE1" t="inlineStr">
+        <is>
+          <t>tipsoft_override_asof</t>
+        </is>
+      </c>
+      <c r="CF1" t="inlineStr">
+        <is>
+          <t>tipsoft_override_ok</t>
+        </is>
+      </c>
+      <c r="CG1" t="inlineStr">
+        <is>
+          <t>tipsoft_override_stale</t>
+        </is>
+      </c>
+      <c r="CH1" t="inlineStr">
+        <is>
+          <t>tipsoft_override_reason</t>
+        </is>
+      </c>
+      <c r="CI1" t="inlineStr">
+        <is>
+          <t>tipsoft_override_panel_tip</t>
+        </is>
+      </c>
+      <c r="CJ1" t="inlineStr">
+        <is>
+          <t>tipsoft_override_return_blend_applied</t>
+        </is>
+      </c>
+      <c r="CK1" t="inlineStr">
+        <is>
+          <t>tipsoft_live_override_path3_within_keep</t>
+        </is>
+      </c>
+      <c r="CL1" t="inlineStr">
+        <is>
+          <t>tipsoft_live_override_soft_fin_tel_stay_off</t>
+        </is>
+      </c>
+      <c r="CM1" t="inlineStr">
+        <is>
+          <t>tipsoft_live_override_path4_live</t>
+        </is>
+      </c>
+      <c r="CN1" t="inlineStr">
+        <is>
+          <t>tipsoft_live_override_broker</t>
         </is>
       </c>
     </row>
@@ -908,6 +998,24 @@
       <c r="BT2" t="inlineStr"/>
       <c r="BU2" t="inlineStr"/>
       <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
+      <c r="CG2" t="inlineStr"/>
+      <c r="CH2" t="inlineStr"/>
+      <c r="CI2" t="inlineStr"/>
+      <c r="CJ2" t="inlineStr"/>
+      <c r="CK2" t="inlineStr"/>
+      <c r="CL2" t="inlineStr"/>
+      <c r="CM2" t="inlineStr"/>
+      <c r="CN2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1026,6 +1134,24 @@
       <c r="BT3" t="inlineStr"/>
       <c r="BU3" t="inlineStr"/>
       <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr"/>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr"/>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr"/>
+      <c r="CC3" t="inlineStr"/>
+      <c r="CD3" t="inlineStr"/>
+      <c r="CE3" t="inlineStr"/>
+      <c r="CF3" t="inlineStr"/>
+      <c r="CG3" t="inlineStr"/>
+      <c r="CH3" t="inlineStr"/>
+      <c r="CI3" t="inlineStr"/>
+      <c r="CJ3" t="inlineStr"/>
+      <c r="CK3" t="inlineStr"/>
+      <c r="CL3" t="inlineStr"/>
+      <c r="CM3" t="inlineStr"/>
+      <c r="CN3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1144,6 +1270,24 @@
       <c r="BT4" t="inlineStr"/>
       <c r="BU4" t="inlineStr"/>
       <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="inlineStr"/>
+      <c r="CD4" t="inlineStr"/>
+      <c r="CE4" t="inlineStr"/>
+      <c r="CF4" t="inlineStr"/>
+      <c r="CG4" t="inlineStr"/>
+      <c r="CH4" t="inlineStr"/>
+      <c r="CI4" t="inlineStr"/>
+      <c r="CJ4" t="inlineStr"/>
+      <c r="CK4" t="inlineStr"/>
+      <c r="CL4" t="inlineStr"/>
+      <c r="CM4" t="inlineStr"/>
+      <c r="CN4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1262,6 +1406,24 @@
       <c r="BT5" t="inlineStr"/>
       <c r="BU5" t="inlineStr"/>
       <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="inlineStr"/>
+      <c r="BX5" t="inlineStr"/>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="inlineStr"/>
+      <c r="CA5" t="inlineStr"/>
+      <c r="CB5" t="inlineStr"/>
+      <c r="CC5" t="inlineStr"/>
+      <c r="CD5" t="inlineStr"/>
+      <c r="CE5" t="inlineStr"/>
+      <c r="CF5" t="inlineStr"/>
+      <c r="CG5" t="inlineStr"/>
+      <c r="CH5" t="inlineStr"/>
+      <c r="CI5" t="inlineStr"/>
+      <c r="CJ5" t="inlineStr"/>
+      <c r="CK5" t="inlineStr"/>
+      <c r="CL5" t="inlineStr"/>
+      <c r="CM5" t="inlineStr"/>
+      <c r="CN5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1380,6 +1542,24 @@
       <c r="BT6" t="inlineStr"/>
       <c r="BU6" t="inlineStr"/>
       <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr"/>
+      <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="inlineStr"/>
+      <c r="CC6" t="inlineStr"/>
+      <c r="CD6" t="inlineStr"/>
+      <c r="CE6" t="inlineStr"/>
+      <c r="CF6" t="inlineStr"/>
+      <c r="CG6" t="inlineStr"/>
+      <c r="CH6" t="inlineStr"/>
+      <c r="CI6" t="inlineStr"/>
+      <c r="CJ6" t="inlineStr"/>
+      <c r="CK6" t="inlineStr"/>
+      <c r="CL6" t="inlineStr"/>
+      <c r="CM6" t="inlineStr"/>
+      <c r="CN6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1498,6 +1678,24 @@
       <c r="BT7" t="inlineStr"/>
       <c r="BU7" t="inlineStr"/>
       <c r="BV7" t="inlineStr"/>
+      <c r="BW7" t="inlineStr"/>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="inlineStr"/>
+      <c r="CA7" t="inlineStr"/>
+      <c r="CB7" t="inlineStr"/>
+      <c r="CC7" t="inlineStr"/>
+      <c r="CD7" t="inlineStr"/>
+      <c r="CE7" t="inlineStr"/>
+      <c r="CF7" t="inlineStr"/>
+      <c r="CG7" t="inlineStr"/>
+      <c r="CH7" t="inlineStr"/>
+      <c r="CI7" t="inlineStr"/>
+      <c r="CJ7" t="inlineStr"/>
+      <c r="CK7" t="inlineStr"/>
+      <c r="CL7" t="inlineStr"/>
+      <c r="CM7" t="inlineStr"/>
+      <c r="CN7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1616,6 +1814,24 @@
       <c r="BT8" t="inlineStr"/>
       <c r="BU8" t="inlineStr"/>
       <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
+      <c r="CA8" t="inlineStr"/>
+      <c r="CB8" t="inlineStr"/>
+      <c r="CC8" t="inlineStr"/>
+      <c r="CD8" t="inlineStr"/>
+      <c r="CE8" t="inlineStr"/>
+      <c r="CF8" t="inlineStr"/>
+      <c r="CG8" t="inlineStr"/>
+      <c r="CH8" t="inlineStr"/>
+      <c r="CI8" t="inlineStr"/>
+      <c r="CJ8" t="inlineStr"/>
+      <c r="CK8" t="inlineStr"/>
+      <c r="CL8" t="inlineStr"/>
+      <c r="CM8" t="inlineStr"/>
+      <c r="CN8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1734,6 +1950,24 @@
       <c r="BT9" t="inlineStr"/>
       <c r="BU9" t="inlineStr"/>
       <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr"/>
+      <c r="CE9" t="inlineStr"/>
+      <c r="CF9" t="inlineStr"/>
+      <c r="CG9" t="inlineStr"/>
+      <c r="CH9" t="inlineStr"/>
+      <c r="CI9" t="inlineStr"/>
+      <c r="CJ9" t="inlineStr"/>
+      <c r="CK9" t="inlineStr"/>
+      <c r="CL9" t="inlineStr"/>
+      <c r="CM9" t="inlineStr"/>
+      <c r="CN9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1852,6 +2086,24 @@
       <c r="BT10" t="inlineStr"/>
       <c r="BU10" t="inlineStr"/>
       <c r="BV10" t="inlineStr"/>
+      <c r="BW10" t="inlineStr"/>
+      <c r="BX10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr"/>
+      <c r="BZ10" t="inlineStr"/>
+      <c r="CA10" t="inlineStr"/>
+      <c r="CB10" t="inlineStr"/>
+      <c r="CC10" t="inlineStr"/>
+      <c r="CD10" t="inlineStr"/>
+      <c r="CE10" t="inlineStr"/>
+      <c r="CF10" t="inlineStr"/>
+      <c r="CG10" t="inlineStr"/>
+      <c r="CH10" t="inlineStr"/>
+      <c r="CI10" t="inlineStr"/>
+      <c r="CJ10" t="inlineStr"/>
+      <c r="CK10" t="inlineStr"/>
+      <c r="CL10" t="inlineStr"/>
+      <c r="CM10" t="inlineStr"/>
+      <c r="CN10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1970,6 +2222,24 @@
       <c r="BT11" t="inlineStr"/>
       <c r="BU11" t="inlineStr"/>
       <c r="BV11" t="inlineStr"/>
+      <c r="BW11" t="inlineStr"/>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="inlineStr"/>
+      <c r="CA11" t="inlineStr"/>
+      <c r="CB11" t="inlineStr"/>
+      <c r="CC11" t="inlineStr"/>
+      <c r="CD11" t="inlineStr"/>
+      <c r="CE11" t="inlineStr"/>
+      <c r="CF11" t="inlineStr"/>
+      <c r="CG11" t="inlineStr"/>
+      <c r="CH11" t="inlineStr"/>
+      <c r="CI11" t="inlineStr"/>
+      <c r="CJ11" t="inlineStr"/>
+      <c r="CK11" t="inlineStr"/>
+      <c r="CL11" t="inlineStr"/>
+      <c r="CM11" t="inlineStr"/>
+      <c r="CN11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2088,6 +2358,24 @@
       <c r="BT12" t="inlineStr"/>
       <c r="BU12" t="inlineStr"/>
       <c r="BV12" t="inlineStr"/>
+      <c r="BW12" t="inlineStr"/>
+      <c r="BX12" t="inlineStr"/>
+      <c r="BY12" t="inlineStr"/>
+      <c r="BZ12" t="inlineStr"/>
+      <c r="CA12" t="inlineStr"/>
+      <c r="CB12" t="inlineStr"/>
+      <c r="CC12" t="inlineStr"/>
+      <c r="CD12" t="inlineStr"/>
+      <c r="CE12" t="inlineStr"/>
+      <c r="CF12" t="inlineStr"/>
+      <c r="CG12" t="inlineStr"/>
+      <c r="CH12" t="inlineStr"/>
+      <c r="CI12" t="inlineStr"/>
+      <c r="CJ12" t="inlineStr"/>
+      <c r="CK12" t="inlineStr"/>
+      <c r="CL12" t="inlineStr"/>
+      <c r="CM12" t="inlineStr"/>
+      <c r="CN12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2206,6 +2494,24 @@
       <c r="BT13" t="inlineStr"/>
       <c r="BU13" t="inlineStr"/>
       <c r="BV13" t="inlineStr"/>
+      <c r="BW13" t="inlineStr"/>
+      <c r="BX13" t="inlineStr"/>
+      <c r="BY13" t="inlineStr"/>
+      <c r="BZ13" t="inlineStr"/>
+      <c r="CA13" t="inlineStr"/>
+      <c r="CB13" t="inlineStr"/>
+      <c r="CC13" t="inlineStr"/>
+      <c r="CD13" t="inlineStr"/>
+      <c r="CE13" t="inlineStr"/>
+      <c r="CF13" t="inlineStr"/>
+      <c r="CG13" t="inlineStr"/>
+      <c r="CH13" t="inlineStr"/>
+      <c r="CI13" t="inlineStr"/>
+      <c r="CJ13" t="inlineStr"/>
+      <c r="CK13" t="inlineStr"/>
+      <c r="CL13" t="inlineStr"/>
+      <c r="CM13" t="inlineStr"/>
+      <c r="CN13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2334,6 +2640,24 @@
       <c r="BT14" t="inlineStr"/>
       <c r="BU14" t="inlineStr"/>
       <c r="BV14" t="inlineStr"/>
+      <c r="BW14" t="inlineStr"/>
+      <c r="BX14" t="inlineStr"/>
+      <c r="BY14" t="inlineStr"/>
+      <c r="BZ14" t="inlineStr"/>
+      <c r="CA14" t="inlineStr"/>
+      <c r="CB14" t="inlineStr"/>
+      <c r="CC14" t="inlineStr"/>
+      <c r="CD14" t="inlineStr"/>
+      <c r="CE14" t="inlineStr"/>
+      <c r="CF14" t="inlineStr"/>
+      <c r="CG14" t="inlineStr"/>
+      <c r="CH14" t="inlineStr"/>
+      <c r="CI14" t="inlineStr"/>
+      <c r="CJ14" t="inlineStr"/>
+      <c r="CK14" t="inlineStr"/>
+      <c r="CL14" t="inlineStr"/>
+      <c r="CM14" t="inlineStr"/>
+      <c r="CN14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2462,6 +2786,24 @@
       <c r="BT15" t="inlineStr"/>
       <c r="BU15" t="inlineStr"/>
       <c r="BV15" t="inlineStr"/>
+      <c r="BW15" t="inlineStr"/>
+      <c r="BX15" t="inlineStr"/>
+      <c r="BY15" t="inlineStr"/>
+      <c r="BZ15" t="inlineStr"/>
+      <c r="CA15" t="inlineStr"/>
+      <c r="CB15" t="inlineStr"/>
+      <c r="CC15" t="inlineStr"/>
+      <c r="CD15" t="inlineStr"/>
+      <c r="CE15" t="inlineStr"/>
+      <c r="CF15" t="inlineStr"/>
+      <c r="CG15" t="inlineStr"/>
+      <c r="CH15" t="inlineStr"/>
+      <c r="CI15" t="inlineStr"/>
+      <c r="CJ15" t="inlineStr"/>
+      <c r="CK15" t="inlineStr"/>
+      <c r="CL15" t="inlineStr"/>
+      <c r="CM15" t="inlineStr"/>
+      <c r="CN15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2590,6 +2932,24 @@
       <c r="BT16" t="inlineStr"/>
       <c r="BU16" t="inlineStr"/>
       <c r="BV16" t="inlineStr"/>
+      <c r="BW16" t="inlineStr"/>
+      <c r="BX16" t="inlineStr"/>
+      <c r="BY16" t="inlineStr"/>
+      <c r="BZ16" t="inlineStr"/>
+      <c r="CA16" t="inlineStr"/>
+      <c r="CB16" t="inlineStr"/>
+      <c r="CC16" t="inlineStr"/>
+      <c r="CD16" t="inlineStr"/>
+      <c r="CE16" t="inlineStr"/>
+      <c r="CF16" t="inlineStr"/>
+      <c r="CG16" t="inlineStr"/>
+      <c r="CH16" t="inlineStr"/>
+      <c r="CI16" t="inlineStr"/>
+      <c r="CJ16" t="inlineStr"/>
+      <c r="CK16" t="inlineStr"/>
+      <c r="CL16" t="inlineStr"/>
+      <c r="CM16" t="inlineStr"/>
+      <c r="CN16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2738,6 +3098,24 @@
       <c r="BT17" t="inlineStr"/>
       <c r="BU17" t="inlineStr"/>
       <c r="BV17" t="inlineStr"/>
+      <c r="BW17" t="inlineStr"/>
+      <c r="BX17" t="inlineStr"/>
+      <c r="BY17" t="inlineStr"/>
+      <c r="BZ17" t="inlineStr"/>
+      <c r="CA17" t="inlineStr"/>
+      <c r="CB17" t="inlineStr"/>
+      <c r="CC17" t="inlineStr"/>
+      <c r="CD17" t="inlineStr"/>
+      <c r="CE17" t="inlineStr"/>
+      <c r="CF17" t="inlineStr"/>
+      <c r="CG17" t="inlineStr"/>
+      <c r="CH17" t="inlineStr"/>
+      <c r="CI17" t="inlineStr"/>
+      <c r="CJ17" t="inlineStr"/>
+      <c r="CK17" t="inlineStr"/>
+      <c r="CL17" t="inlineStr"/>
+      <c r="CM17" t="inlineStr"/>
+      <c r="CN17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2886,6 +3264,24 @@
       <c r="BT18" t="inlineStr"/>
       <c r="BU18" t="inlineStr"/>
       <c r="BV18" t="inlineStr"/>
+      <c r="BW18" t="inlineStr"/>
+      <c r="BX18" t="inlineStr"/>
+      <c r="BY18" t="inlineStr"/>
+      <c r="BZ18" t="inlineStr"/>
+      <c r="CA18" t="inlineStr"/>
+      <c r="CB18" t="inlineStr"/>
+      <c r="CC18" t="inlineStr"/>
+      <c r="CD18" t="inlineStr"/>
+      <c r="CE18" t="inlineStr"/>
+      <c r="CF18" t="inlineStr"/>
+      <c r="CG18" t="inlineStr"/>
+      <c r="CH18" t="inlineStr"/>
+      <c r="CI18" t="inlineStr"/>
+      <c r="CJ18" t="inlineStr"/>
+      <c r="CK18" t="inlineStr"/>
+      <c r="CL18" t="inlineStr"/>
+      <c r="CM18" t="inlineStr"/>
+      <c r="CN18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3034,6 +3430,24 @@
       <c r="BT19" t="inlineStr"/>
       <c r="BU19" t="inlineStr"/>
       <c r="BV19" t="inlineStr"/>
+      <c r="BW19" t="inlineStr"/>
+      <c r="BX19" t="inlineStr"/>
+      <c r="BY19" t="inlineStr"/>
+      <c r="BZ19" t="inlineStr"/>
+      <c r="CA19" t="inlineStr"/>
+      <c r="CB19" t="inlineStr"/>
+      <c r="CC19" t="inlineStr"/>
+      <c r="CD19" t="inlineStr"/>
+      <c r="CE19" t="inlineStr"/>
+      <c r="CF19" t="inlineStr"/>
+      <c r="CG19" t="inlineStr"/>
+      <c r="CH19" t="inlineStr"/>
+      <c r="CI19" t="inlineStr"/>
+      <c r="CJ19" t="inlineStr"/>
+      <c r="CK19" t="inlineStr"/>
+      <c r="CL19" t="inlineStr"/>
+      <c r="CM19" t="inlineStr"/>
+      <c r="CN19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3186,6 +3600,24 @@
       <c r="BT20" t="inlineStr"/>
       <c r="BU20" t="inlineStr"/>
       <c r="BV20" t="inlineStr"/>
+      <c r="BW20" t="inlineStr"/>
+      <c r="BX20" t="inlineStr"/>
+      <c r="BY20" t="inlineStr"/>
+      <c r="BZ20" t="inlineStr"/>
+      <c r="CA20" t="inlineStr"/>
+      <c r="CB20" t="inlineStr"/>
+      <c r="CC20" t="inlineStr"/>
+      <c r="CD20" t="inlineStr"/>
+      <c r="CE20" t="inlineStr"/>
+      <c r="CF20" t="inlineStr"/>
+      <c r="CG20" t="inlineStr"/>
+      <c r="CH20" t="inlineStr"/>
+      <c r="CI20" t="inlineStr"/>
+      <c r="CJ20" t="inlineStr"/>
+      <c r="CK20" t="inlineStr"/>
+      <c r="CL20" t="inlineStr"/>
+      <c r="CM20" t="inlineStr"/>
+      <c r="CN20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3338,6 +3770,24 @@
       <c r="BT21" t="inlineStr"/>
       <c r="BU21" t="inlineStr"/>
       <c r="BV21" t="inlineStr"/>
+      <c r="BW21" t="inlineStr"/>
+      <c r="BX21" t="inlineStr"/>
+      <c r="BY21" t="inlineStr"/>
+      <c r="BZ21" t="inlineStr"/>
+      <c r="CA21" t="inlineStr"/>
+      <c r="CB21" t="inlineStr"/>
+      <c r="CC21" t="inlineStr"/>
+      <c r="CD21" t="inlineStr"/>
+      <c r="CE21" t="inlineStr"/>
+      <c r="CF21" t="inlineStr"/>
+      <c r="CG21" t="inlineStr"/>
+      <c r="CH21" t="inlineStr"/>
+      <c r="CI21" t="inlineStr"/>
+      <c r="CJ21" t="inlineStr"/>
+      <c r="CK21" t="inlineStr"/>
+      <c r="CL21" t="inlineStr"/>
+      <c r="CM21" t="inlineStr"/>
+      <c r="CN21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3490,6 +3940,24 @@
       <c r="BT22" t="inlineStr"/>
       <c r="BU22" t="inlineStr"/>
       <c r="BV22" t="inlineStr"/>
+      <c r="BW22" t="inlineStr"/>
+      <c r="BX22" t="inlineStr"/>
+      <c r="BY22" t="inlineStr"/>
+      <c r="BZ22" t="inlineStr"/>
+      <c r="CA22" t="inlineStr"/>
+      <c r="CB22" t="inlineStr"/>
+      <c r="CC22" t="inlineStr"/>
+      <c r="CD22" t="inlineStr"/>
+      <c r="CE22" t="inlineStr"/>
+      <c r="CF22" t="inlineStr"/>
+      <c r="CG22" t="inlineStr"/>
+      <c r="CH22" t="inlineStr"/>
+      <c r="CI22" t="inlineStr"/>
+      <c r="CJ22" t="inlineStr"/>
+      <c r="CK22" t="inlineStr"/>
+      <c r="CL22" t="inlineStr"/>
+      <c r="CM22" t="inlineStr"/>
+      <c r="CN22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3642,6 +4110,24 @@
       <c r="BT23" t="inlineStr"/>
       <c r="BU23" t="inlineStr"/>
       <c r="BV23" t="inlineStr"/>
+      <c r="BW23" t="inlineStr"/>
+      <c r="BX23" t="inlineStr"/>
+      <c r="BY23" t="inlineStr"/>
+      <c r="BZ23" t="inlineStr"/>
+      <c r="CA23" t="inlineStr"/>
+      <c r="CB23" t="inlineStr"/>
+      <c r="CC23" t="inlineStr"/>
+      <c r="CD23" t="inlineStr"/>
+      <c r="CE23" t="inlineStr"/>
+      <c r="CF23" t="inlineStr"/>
+      <c r="CG23" t="inlineStr"/>
+      <c r="CH23" t="inlineStr"/>
+      <c r="CI23" t="inlineStr"/>
+      <c r="CJ23" t="inlineStr"/>
+      <c r="CK23" t="inlineStr"/>
+      <c r="CL23" t="inlineStr"/>
+      <c r="CM23" t="inlineStr"/>
+      <c r="CN23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3876,6 +4362,24 @@
       <c r="BT24" t="inlineStr"/>
       <c r="BU24" t="inlineStr"/>
       <c r="BV24" t="inlineStr"/>
+      <c r="BW24" t="inlineStr"/>
+      <c r="BX24" t="inlineStr"/>
+      <c r="BY24" t="inlineStr"/>
+      <c r="BZ24" t="inlineStr"/>
+      <c r="CA24" t="inlineStr"/>
+      <c r="CB24" t="inlineStr"/>
+      <c r="CC24" t="inlineStr"/>
+      <c r="CD24" t="inlineStr"/>
+      <c r="CE24" t="inlineStr"/>
+      <c r="CF24" t="inlineStr"/>
+      <c r="CG24" t="inlineStr"/>
+      <c r="CH24" t="inlineStr"/>
+      <c r="CI24" t="inlineStr"/>
+      <c r="CJ24" t="inlineStr"/>
+      <c r="CK24" t="inlineStr"/>
+      <c r="CL24" t="inlineStr"/>
+      <c r="CM24" t="inlineStr"/>
+      <c r="CN24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4131,6 +4635,353 @@
       </c>
       <c r="BV25" t="n">
         <v>5</v>
+      </c>
+      <c r="BW25" t="inlineStr"/>
+      <c r="BX25" t="inlineStr"/>
+      <c r="BY25" t="inlineStr"/>
+      <c r="BZ25" t="inlineStr"/>
+      <c r="CA25" t="inlineStr"/>
+      <c r="CB25" t="inlineStr"/>
+      <c r="CC25" t="inlineStr"/>
+      <c r="CD25" t="inlineStr"/>
+      <c r="CE25" t="inlineStr"/>
+      <c r="CF25" t="inlineStr"/>
+      <c r="CG25" t="inlineStr"/>
+      <c r="CH25" t="inlineStr"/>
+      <c r="CI25" t="inlineStr"/>
+      <c r="CJ25" t="inlineStr"/>
+      <c r="CK25" t="inlineStr"/>
+      <c r="CL25" t="inlineStr"/>
+      <c r="CM25" t="inlineStr"/>
+      <c r="CN25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-10-01T15:36:48.837112+00:00</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0012235067050874</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.5086302715497426</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-0.50985377825483</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.7549897760494932</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.1526640167411745</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.09234620720933211</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.7549897760493324</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.1526640167413354</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.0923462072093322</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>FIN_DUAL_PUB_PRIV</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>KD_APR15_MAY15_Klt30_T15</t>
+        </is>
+      </c>
+      <c r="T26" t="b">
+        <v>0</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: COOL_c8_f50_d21 (replace DH, keep FUSE)</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>ACCEPT_2026-09-09_DROP_E45_A05</t>
+        </is>
+      </c>
+      <c r="AG26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>COOL_c8_f50_d21</t>
+        </is>
+      </c>
+      <c r="AI26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0.7549897760494932</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0.1526640167411745</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0.09234620720933211</v>
+      </c>
+      <c r="AM26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>ACCEPT Class D: FinPriv V7 F05</t>
+        </is>
+      </c>
+      <c r="AO26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AQ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: CONF_RET3_A10_H5 (00631L short-assist under COOL)</t>
+        </is>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>ACCEPT Live Path3 switch emitter: T0_CARVE_FIN_SAT_SWITCH tagged orders (P3_T0_STATE · Soft-Frozen Exact T+1 KEEP elsewhere · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>weight_engine_not_wired</t>
+        </is>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>ledger</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>ACCEPT Path3 weight engine: P3_COMP_SAT_DAILY_POS_LEDGER_A (ledger-scaled recon · Soft 0050 KEEP · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>P3_COMP_SAT_DAILY_POS_LEDGER_A</t>
+        </is>
+      </c>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>ledger_stale</t>
+        </is>
+      </c>
+      <c r="BE26" t="inlineStr"/>
+      <c r="BF26" t="b">
+        <v>1</v>
+      </c>
+      <c r="BG26" t="inlineStr">
+        <is>
+          <t>ACCEPT Soft↔Path3 coexist mute: MUTE_SOFT_FIN_TEL (flip-day Soft FIN/TEL Exact T+1 muted · Soft 0050 KEEP · Path3 -P3T0 KEEP · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>MUTE_SOFT_FIN_TEL</t>
+        </is>
+      </c>
+      <c r="BI26" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK26" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL26" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: T3_COOL_INV_VOL20 (TEL within-sleeve under COOL)</t>
+        </is>
+      </c>
+      <c r="BM26" t="inlineStr">
+        <is>
+          <t>TEL_EQUAL</t>
+        </is>
+      </c>
+      <c r="BN26" t="b">
+        <v>0</v>
+      </c>
+      <c r="BO26" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP26" t="inlineStr">
+        <is>
+          <t>LIVE_TEL_T3_COOL_INV_VOL20</t>
+        </is>
+      </c>
+      <c r="BQ26" t="b">
+        <v>1</v>
+      </c>
+      <c r="BR26" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS26" t="inlineStr">
+        <is>
+          <t>WITHIN_SLEEVE_PATH3</t>
+        </is>
+      </c>
+      <c r="BT26" t="inlineStr">
+        <is>
+          <t>ACCEPT Path3 strategy cutover: WITHIN_SLEEVE_PATH3
+(Soft clips+0050 Exact T+1 KEEP · Soft FIN/TEL Exact T+1 OFF · Path3 ledger daily ·
+ T0_CARVE_FIN_SAT_SWITCH KEEP · broker false · overlays KEEP)</t>
+        </is>
+      </c>
+      <c r="BU26" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV26" t="n">
+        <v>5</v>
+      </c>
+      <c r="BW26" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX26" t="inlineStr">
+        <is>
+          <t>gate_stamps_telemetry</t>
+        </is>
+      </c>
+      <c r="BY26" t="inlineStr">
+        <is>
+          <t>TIPSOFT_P3_LIVE_OVERRIDE_W42_M05_K3</t>
+        </is>
+      </c>
+      <c r="BZ26" t="inlineStr">
+        <is>
+          <t>OVERRIDE_LIVE_W42_M0005_K3</t>
+        </is>
+      </c>
+      <c r="CA26" t="inlineStr">
+        <is>
+          <t>ACCEPT live wire: TIPSOFT_P3_LIVE_OVERRIDE_W42_M05_K3
+(Exact T+1 · 0kb1 MUTE_S3_SAT + force LIVE when lag42 live leads champ by &gt;0.5% for 3d ·
+ Path3 WITHIN_SLEEVE KEEP · Soft FIN/TEL stay OFF · Soft clips+0050 KEEP ·
+ T0_CARVE_FIN_SAT_SWITCH KEEP · Path4 OFF · broker false · dual-paper observe KEEP)</t>
+        </is>
+      </c>
+      <c r="CB26" t="inlineStr">
+        <is>
+          <t>ACCEPT_2026-09-30_TIPSOFT_P3_LIVE_OVERRIDE_W42_M05_K3</t>
+        </is>
+      </c>
+      <c r="CC26" t="inlineStr">
+        <is>
+          <t>Set LIVE.live_tipsoft_live_override=False (live_config.live_tipsoft_live_override); tip Soft Exact T+1 LIVE_OVERRIDE gate stamps off; Path3 WITHIN / Soft FIN/TEL unchanged</t>
+        </is>
+      </c>
+      <c r="CD26" t="inlineStr"/>
+      <c r="CE26" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="CF26" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG26" t="b">
+        <v>1</v>
+      </c>
+      <c r="CH26" t="inlineStr">
+        <is>
+          <t>nav_stale</t>
+        </is>
+      </c>
+      <c r="CI26" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="CJ26" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK26" t="b">
+        <v>1</v>
+      </c>
+      <c r="CL26" t="b">
+        <v>1</v>
+      </c>
+      <c r="CM26" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN26" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4144,7 +4995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S25"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5557,6 +6408,69 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>538702112.698374</v>
+      </c>
+      <c r="C26" t="n">
+        <v>18280512.69837398</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.7871680656233667</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0877312319479653</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.0911663400650112</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.09829094151140361</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="b">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>E22_v3_recv_pay_effdelay</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5571,7 +6485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8282,6 +9196,32 @@
       </c>
       <c r="F104" t="n">
         <v>112.05</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-10-01-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>50</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>4000</v>
+      </c>
+      <c r="F105" t="n">
+        <v>112.9</v>
       </c>
     </row>
   </sheetData>
@@ -8295,7 +9235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12430,6 +13370,46 @@
         <v>5</v>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-09-30-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>50</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>27000</v>
+      </c>
+      <c r="G104" t="n">
+        <v>112.2561</v>
+      </c>
+      <c r="H104" t="n">
+        <v>3030914.7</v>
+      </c>
+      <c r="I104" t="n">
+        <v>2591.4320685</v>
+      </c>
+      <c r="J104" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CN26"/>
+  <dimension ref="A1:DI27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -878,6 +878,111 @@
       <c r="CN1" t="inlineStr">
         <is>
           <t>tipsoft_live_override_broker</t>
+        </is>
+      </c>
+      <c r="CO1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_switch_live</t>
+        </is>
+      </c>
+      <c r="CP1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_switch_wire_mode</t>
+        </is>
+      </c>
+      <c r="CQ1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_switch_policy</t>
+        </is>
+      </c>
+      <c r="CR1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_switch_stage_a_arm</t>
+        </is>
+      </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_switch_ballot</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_switch_cutover</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_switch_rollback</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_want_trail</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_trail42_on</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_path3_active</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_fill</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_asof</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_ok</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_stale</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_reason</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_panel_tip</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_return_blend_applied</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_switch_path3_within_keep</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_switch_soft_fin_tel_stay_off</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_switch_path4_live</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>tipsoft_dd_switch_broker</t>
         </is>
       </c>
     </row>
@@ -1016,6 +1121,27 @@
       <c r="CL2" t="inlineStr"/>
       <c r="CM2" t="inlineStr"/>
       <c r="CN2" t="inlineStr"/>
+      <c r="CO2" t="inlineStr"/>
+      <c r="CP2" t="inlineStr"/>
+      <c r="CQ2" t="inlineStr"/>
+      <c r="CR2" t="inlineStr"/>
+      <c r="CS2" t="inlineStr"/>
+      <c r="CT2" t="inlineStr"/>
+      <c r="CU2" t="inlineStr"/>
+      <c r="CV2" t="inlineStr"/>
+      <c r="CW2" t="inlineStr"/>
+      <c r="CX2" t="inlineStr"/>
+      <c r="CY2" t="inlineStr"/>
+      <c r="CZ2" t="inlineStr"/>
+      <c r="DA2" t="inlineStr"/>
+      <c r="DB2" t="inlineStr"/>
+      <c r="DC2" t="inlineStr"/>
+      <c r="DD2" t="inlineStr"/>
+      <c r="DE2" t="inlineStr"/>
+      <c r="DF2" t="inlineStr"/>
+      <c r="DG2" t="inlineStr"/>
+      <c r="DH2" t="inlineStr"/>
+      <c r="DI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1152,6 +1278,27 @@
       <c r="CL3" t="inlineStr"/>
       <c r="CM3" t="inlineStr"/>
       <c r="CN3" t="inlineStr"/>
+      <c r="CO3" t="inlineStr"/>
+      <c r="CP3" t="inlineStr"/>
+      <c r="CQ3" t="inlineStr"/>
+      <c r="CR3" t="inlineStr"/>
+      <c r="CS3" t="inlineStr"/>
+      <c r="CT3" t="inlineStr"/>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr"/>
+      <c r="CW3" t="inlineStr"/>
+      <c r="CX3" t="inlineStr"/>
+      <c r="CY3" t="inlineStr"/>
+      <c r="CZ3" t="inlineStr"/>
+      <c r="DA3" t="inlineStr"/>
+      <c r="DB3" t="inlineStr"/>
+      <c r="DC3" t="inlineStr"/>
+      <c r="DD3" t="inlineStr"/>
+      <c r="DE3" t="inlineStr"/>
+      <c r="DF3" t="inlineStr"/>
+      <c r="DG3" t="inlineStr"/>
+      <c r="DH3" t="inlineStr"/>
+      <c r="DI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1288,6 +1435,27 @@
       <c r="CL4" t="inlineStr"/>
       <c r="CM4" t="inlineStr"/>
       <c r="CN4" t="inlineStr"/>
+      <c r="CO4" t="inlineStr"/>
+      <c r="CP4" t="inlineStr"/>
+      <c r="CQ4" t="inlineStr"/>
+      <c r="CR4" t="inlineStr"/>
+      <c r="CS4" t="inlineStr"/>
+      <c r="CT4" t="inlineStr"/>
+      <c r="CU4" t="inlineStr"/>
+      <c r="CV4" t="inlineStr"/>
+      <c r="CW4" t="inlineStr"/>
+      <c r="CX4" t="inlineStr"/>
+      <c r="CY4" t="inlineStr"/>
+      <c r="CZ4" t="inlineStr"/>
+      <c r="DA4" t="inlineStr"/>
+      <c r="DB4" t="inlineStr"/>
+      <c r="DC4" t="inlineStr"/>
+      <c r="DD4" t="inlineStr"/>
+      <c r="DE4" t="inlineStr"/>
+      <c r="DF4" t="inlineStr"/>
+      <c r="DG4" t="inlineStr"/>
+      <c r="DH4" t="inlineStr"/>
+      <c r="DI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1424,6 +1592,27 @@
       <c r="CL5" t="inlineStr"/>
       <c r="CM5" t="inlineStr"/>
       <c r="CN5" t="inlineStr"/>
+      <c r="CO5" t="inlineStr"/>
+      <c r="CP5" t="inlineStr"/>
+      <c r="CQ5" t="inlineStr"/>
+      <c r="CR5" t="inlineStr"/>
+      <c r="CS5" t="inlineStr"/>
+      <c r="CT5" t="inlineStr"/>
+      <c r="CU5" t="inlineStr"/>
+      <c r="CV5" t="inlineStr"/>
+      <c r="CW5" t="inlineStr"/>
+      <c r="CX5" t="inlineStr"/>
+      <c r="CY5" t="inlineStr"/>
+      <c r="CZ5" t="inlineStr"/>
+      <c r="DA5" t="inlineStr"/>
+      <c r="DB5" t="inlineStr"/>
+      <c r="DC5" t="inlineStr"/>
+      <c r="DD5" t="inlineStr"/>
+      <c r="DE5" t="inlineStr"/>
+      <c r="DF5" t="inlineStr"/>
+      <c r="DG5" t="inlineStr"/>
+      <c r="DH5" t="inlineStr"/>
+      <c r="DI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1560,6 +1749,27 @@
       <c r="CL6" t="inlineStr"/>
       <c r="CM6" t="inlineStr"/>
       <c r="CN6" t="inlineStr"/>
+      <c r="CO6" t="inlineStr"/>
+      <c r="CP6" t="inlineStr"/>
+      <c r="CQ6" t="inlineStr"/>
+      <c r="CR6" t="inlineStr"/>
+      <c r="CS6" t="inlineStr"/>
+      <c r="CT6" t="inlineStr"/>
+      <c r="CU6" t="inlineStr"/>
+      <c r="CV6" t="inlineStr"/>
+      <c r="CW6" t="inlineStr"/>
+      <c r="CX6" t="inlineStr"/>
+      <c r="CY6" t="inlineStr"/>
+      <c r="CZ6" t="inlineStr"/>
+      <c r="DA6" t="inlineStr"/>
+      <c r="DB6" t="inlineStr"/>
+      <c r="DC6" t="inlineStr"/>
+      <c r="DD6" t="inlineStr"/>
+      <c r="DE6" t="inlineStr"/>
+      <c r="DF6" t="inlineStr"/>
+      <c r="DG6" t="inlineStr"/>
+      <c r="DH6" t="inlineStr"/>
+      <c r="DI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1696,6 +1906,27 @@
       <c r="CL7" t="inlineStr"/>
       <c r="CM7" t="inlineStr"/>
       <c r="CN7" t="inlineStr"/>
+      <c r="CO7" t="inlineStr"/>
+      <c r="CP7" t="inlineStr"/>
+      <c r="CQ7" t="inlineStr"/>
+      <c r="CR7" t="inlineStr"/>
+      <c r="CS7" t="inlineStr"/>
+      <c r="CT7" t="inlineStr"/>
+      <c r="CU7" t="inlineStr"/>
+      <c r="CV7" t="inlineStr"/>
+      <c r="CW7" t="inlineStr"/>
+      <c r="CX7" t="inlineStr"/>
+      <c r="CY7" t="inlineStr"/>
+      <c r="CZ7" t="inlineStr"/>
+      <c r="DA7" t="inlineStr"/>
+      <c r="DB7" t="inlineStr"/>
+      <c r="DC7" t="inlineStr"/>
+      <c r="DD7" t="inlineStr"/>
+      <c r="DE7" t="inlineStr"/>
+      <c r="DF7" t="inlineStr"/>
+      <c r="DG7" t="inlineStr"/>
+      <c r="DH7" t="inlineStr"/>
+      <c r="DI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1832,6 +2063,27 @@
       <c r="CL8" t="inlineStr"/>
       <c r="CM8" t="inlineStr"/>
       <c r="CN8" t="inlineStr"/>
+      <c r="CO8" t="inlineStr"/>
+      <c r="CP8" t="inlineStr"/>
+      <c r="CQ8" t="inlineStr"/>
+      <c r="CR8" t="inlineStr"/>
+      <c r="CS8" t="inlineStr"/>
+      <c r="CT8" t="inlineStr"/>
+      <c r="CU8" t="inlineStr"/>
+      <c r="CV8" t="inlineStr"/>
+      <c r="CW8" t="inlineStr"/>
+      <c r="CX8" t="inlineStr"/>
+      <c r="CY8" t="inlineStr"/>
+      <c r="CZ8" t="inlineStr"/>
+      <c r="DA8" t="inlineStr"/>
+      <c r="DB8" t="inlineStr"/>
+      <c r="DC8" t="inlineStr"/>
+      <c r="DD8" t="inlineStr"/>
+      <c r="DE8" t="inlineStr"/>
+      <c r="DF8" t="inlineStr"/>
+      <c r="DG8" t="inlineStr"/>
+      <c r="DH8" t="inlineStr"/>
+      <c r="DI8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1968,6 +2220,27 @@
       <c r="CL9" t="inlineStr"/>
       <c r="CM9" t="inlineStr"/>
       <c r="CN9" t="inlineStr"/>
+      <c r="CO9" t="inlineStr"/>
+      <c r="CP9" t="inlineStr"/>
+      <c r="CQ9" t="inlineStr"/>
+      <c r="CR9" t="inlineStr"/>
+      <c r="CS9" t="inlineStr"/>
+      <c r="CT9" t="inlineStr"/>
+      <c r="CU9" t="inlineStr"/>
+      <c r="CV9" t="inlineStr"/>
+      <c r="CW9" t="inlineStr"/>
+      <c r="CX9" t="inlineStr"/>
+      <c r="CY9" t="inlineStr"/>
+      <c r="CZ9" t="inlineStr"/>
+      <c r="DA9" t="inlineStr"/>
+      <c r="DB9" t="inlineStr"/>
+      <c r="DC9" t="inlineStr"/>
+      <c r="DD9" t="inlineStr"/>
+      <c r="DE9" t="inlineStr"/>
+      <c r="DF9" t="inlineStr"/>
+      <c r="DG9" t="inlineStr"/>
+      <c r="DH9" t="inlineStr"/>
+      <c r="DI9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2104,6 +2377,27 @@
       <c r="CL10" t="inlineStr"/>
       <c r="CM10" t="inlineStr"/>
       <c r="CN10" t="inlineStr"/>
+      <c r="CO10" t="inlineStr"/>
+      <c r="CP10" t="inlineStr"/>
+      <c r="CQ10" t="inlineStr"/>
+      <c r="CR10" t="inlineStr"/>
+      <c r="CS10" t="inlineStr"/>
+      <c r="CT10" t="inlineStr"/>
+      <c r="CU10" t="inlineStr"/>
+      <c r="CV10" t="inlineStr"/>
+      <c r="CW10" t="inlineStr"/>
+      <c r="CX10" t="inlineStr"/>
+      <c r="CY10" t="inlineStr"/>
+      <c r="CZ10" t="inlineStr"/>
+      <c r="DA10" t="inlineStr"/>
+      <c r="DB10" t="inlineStr"/>
+      <c r="DC10" t="inlineStr"/>
+      <c r="DD10" t="inlineStr"/>
+      <c r="DE10" t="inlineStr"/>
+      <c r="DF10" t="inlineStr"/>
+      <c r="DG10" t="inlineStr"/>
+      <c r="DH10" t="inlineStr"/>
+      <c r="DI10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2240,6 +2534,27 @@
       <c r="CL11" t="inlineStr"/>
       <c r="CM11" t="inlineStr"/>
       <c r="CN11" t="inlineStr"/>
+      <c r="CO11" t="inlineStr"/>
+      <c r="CP11" t="inlineStr"/>
+      <c r="CQ11" t="inlineStr"/>
+      <c r="CR11" t="inlineStr"/>
+      <c r="CS11" t="inlineStr"/>
+      <c r="CT11" t="inlineStr"/>
+      <c r="CU11" t="inlineStr"/>
+      <c r="CV11" t="inlineStr"/>
+      <c r="CW11" t="inlineStr"/>
+      <c r="CX11" t="inlineStr"/>
+      <c r="CY11" t="inlineStr"/>
+      <c r="CZ11" t="inlineStr"/>
+      <c r="DA11" t="inlineStr"/>
+      <c r="DB11" t="inlineStr"/>
+      <c r="DC11" t="inlineStr"/>
+      <c r="DD11" t="inlineStr"/>
+      <c r="DE11" t="inlineStr"/>
+      <c r="DF11" t="inlineStr"/>
+      <c r="DG11" t="inlineStr"/>
+      <c r="DH11" t="inlineStr"/>
+      <c r="DI11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2376,6 +2691,27 @@
       <c r="CL12" t="inlineStr"/>
       <c r="CM12" t="inlineStr"/>
       <c r="CN12" t="inlineStr"/>
+      <c r="CO12" t="inlineStr"/>
+      <c r="CP12" t="inlineStr"/>
+      <c r="CQ12" t="inlineStr"/>
+      <c r="CR12" t="inlineStr"/>
+      <c r="CS12" t="inlineStr"/>
+      <c r="CT12" t="inlineStr"/>
+      <c r="CU12" t="inlineStr"/>
+      <c r="CV12" t="inlineStr"/>
+      <c r="CW12" t="inlineStr"/>
+      <c r="CX12" t="inlineStr"/>
+      <c r="CY12" t="inlineStr"/>
+      <c r="CZ12" t="inlineStr"/>
+      <c r="DA12" t="inlineStr"/>
+      <c r="DB12" t="inlineStr"/>
+      <c r="DC12" t="inlineStr"/>
+      <c r="DD12" t="inlineStr"/>
+      <c r="DE12" t="inlineStr"/>
+      <c r="DF12" t="inlineStr"/>
+      <c r="DG12" t="inlineStr"/>
+      <c r="DH12" t="inlineStr"/>
+      <c r="DI12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2512,6 +2848,27 @@
       <c r="CL13" t="inlineStr"/>
       <c r="CM13" t="inlineStr"/>
       <c r="CN13" t="inlineStr"/>
+      <c r="CO13" t="inlineStr"/>
+      <c r="CP13" t="inlineStr"/>
+      <c r="CQ13" t="inlineStr"/>
+      <c r="CR13" t="inlineStr"/>
+      <c r="CS13" t="inlineStr"/>
+      <c r="CT13" t="inlineStr"/>
+      <c r="CU13" t="inlineStr"/>
+      <c r="CV13" t="inlineStr"/>
+      <c r="CW13" t="inlineStr"/>
+      <c r="CX13" t="inlineStr"/>
+      <c r="CY13" t="inlineStr"/>
+      <c r="CZ13" t="inlineStr"/>
+      <c r="DA13" t="inlineStr"/>
+      <c r="DB13" t="inlineStr"/>
+      <c r="DC13" t="inlineStr"/>
+      <c r="DD13" t="inlineStr"/>
+      <c r="DE13" t="inlineStr"/>
+      <c r="DF13" t="inlineStr"/>
+      <c r="DG13" t="inlineStr"/>
+      <c r="DH13" t="inlineStr"/>
+      <c r="DI13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2658,6 +3015,27 @@
       <c r="CL14" t="inlineStr"/>
       <c r="CM14" t="inlineStr"/>
       <c r="CN14" t="inlineStr"/>
+      <c r="CO14" t="inlineStr"/>
+      <c r="CP14" t="inlineStr"/>
+      <c r="CQ14" t="inlineStr"/>
+      <c r="CR14" t="inlineStr"/>
+      <c r="CS14" t="inlineStr"/>
+      <c r="CT14" t="inlineStr"/>
+      <c r="CU14" t="inlineStr"/>
+      <c r="CV14" t="inlineStr"/>
+      <c r="CW14" t="inlineStr"/>
+      <c r="CX14" t="inlineStr"/>
+      <c r="CY14" t="inlineStr"/>
+      <c r="CZ14" t="inlineStr"/>
+      <c r="DA14" t="inlineStr"/>
+      <c r="DB14" t="inlineStr"/>
+      <c r="DC14" t="inlineStr"/>
+      <c r="DD14" t="inlineStr"/>
+      <c r="DE14" t="inlineStr"/>
+      <c r="DF14" t="inlineStr"/>
+      <c r="DG14" t="inlineStr"/>
+      <c r="DH14" t="inlineStr"/>
+      <c r="DI14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2804,6 +3182,27 @@
       <c r="CL15" t="inlineStr"/>
       <c r="CM15" t="inlineStr"/>
       <c r="CN15" t="inlineStr"/>
+      <c r="CO15" t="inlineStr"/>
+      <c r="CP15" t="inlineStr"/>
+      <c r="CQ15" t="inlineStr"/>
+      <c r="CR15" t="inlineStr"/>
+      <c r="CS15" t="inlineStr"/>
+      <c r="CT15" t="inlineStr"/>
+      <c r="CU15" t="inlineStr"/>
+      <c r="CV15" t="inlineStr"/>
+      <c r="CW15" t="inlineStr"/>
+      <c r="CX15" t="inlineStr"/>
+      <c r="CY15" t="inlineStr"/>
+      <c r="CZ15" t="inlineStr"/>
+      <c r="DA15" t="inlineStr"/>
+      <c r="DB15" t="inlineStr"/>
+      <c r="DC15" t="inlineStr"/>
+      <c r="DD15" t="inlineStr"/>
+      <c r="DE15" t="inlineStr"/>
+      <c r="DF15" t="inlineStr"/>
+      <c r="DG15" t="inlineStr"/>
+      <c r="DH15" t="inlineStr"/>
+      <c r="DI15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2950,6 +3349,27 @@
       <c r="CL16" t="inlineStr"/>
       <c r="CM16" t="inlineStr"/>
       <c r="CN16" t="inlineStr"/>
+      <c r="CO16" t="inlineStr"/>
+      <c r="CP16" t="inlineStr"/>
+      <c r="CQ16" t="inlineStr"/>
+      <c r="CR16" t="inlineStr"/>
+      <c r="CS16" t="inlineStr"/>
+      <c r="CT16" t="inlineStr"/>
+      <c r="CU16" t="inlineStr"/>
+      <c r="CV16" t="inlineStr"/>
+      <c r="CW16" t="inlineStr"/>
+      <c r="CX16" t="inlineStr"/>
+      <c r="CY16" t="inlineStr"/>
+      <c r="CZ16" t="inlineStr"/>
+      <c r="DA16" t="inlineStr"/>
+      <c r="DB16" t="inlineStr"/>
+      <c r="DC16" t="inlineStr"/>
+      <c r="DD16" t="inlineStr"/>
+      <c r="DE16" t="inlineStr"/>
+      <c r="DF16" t="inlineStr"/>
+      <c r="DG16" t="inlineStr"/>
+      <c r="DH16" t="inlineStr"/>
+      <c r="DI16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3116,6 +3536,27 @@
       <c r="CL17" t="inlineStr"/>
       <c r="CM17" t="inlineStr"/>
       <c r="CN17" t="inlineStr"/>
+      <c r="CO17" t="inlineStr"/>
+      <c r="CP17" t="inlineStr"/>
+      <c r="CQ17" t="inlineStr"/>
+      <c r="CR17" t="inlineStr"/>
+      <c r="CS17" t="inlineStr"/>
+      <c r="CT17" t="inlineStr"/>
+      <c r="CU17" t="inlineStr"/>
+      <c r="CV17" t="inlineStr"/>
+      <c r="CW17" t="inlineStr"/>
+      <c r="CX17" t="inlineStr"/>
+      <c r="CY17" t="inlineStr"/>
+      <c r="CZ17" t="inlineStr"/>
+      <c r="DA17" t="inlineStr"/>
+      <c r="DB17" t="inlineStr"/>
+      <c r="DC17" t="inlineStr"/>
+      <c r="DD17" t="inlineStr"/>
+      <c r="DE17" t="inlineStr"/>
+      <c r="DF17" t="inlineStr"/>
+      <c r="DG17" t="inlineStr"/>
+      <c r="DH17" t="inlineStr"/>
+      <c r="DI17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3282,6 +3723,27 @@
       <c r="CL18" t="inlineStr"/>
       <c r="CM18" t="inlineStr"/>
       <c r="CN18" t="inlineStr"/>
+      <c r="CO18" t="inlineStr"/>
+      <c r="CP18" t="inlineStr"/>
+      <c r="CQ18" t="inlineStr"/>
+      <c r="CR18" t="inlineStr"/>
+      <c r="CS18" t="inlineStr"/>
+      <c r="CT18" t="inlineStr"/>
+      <c r="CU18" t="inlineStr"/>
+      <c r="CV18" t="inlineStr"/>
+      <c r="CW18" t="inlineStr"/>
+      <c r="CX18" t="inlineStr"/>
+      <c r="CY18" t="inlineStr"/>
+      <c r="CZ18" t="inlineStr"/>
+      <c r="DA18" t="inlineStr"/>
+      <c r="DB18" t="inlineStr"/>
+      <c r="DC18" t="inlineStr"/>
+      <c r="DD18" t="inlineStr"/>
+      <c r="DE18" t="inlineStr"/>
+      <c r="DF18" t="inlineStr"/>
+      <c r="DG18" t="inlineStr"/>
+      <c r="DH18" t="inlineStr"/>
+      <c r="DI18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3448,6 +3910,27 @@
       <c r="CL19" t="inlineStr"/>
       <c r="CM19" t="inlineStr"/>
       <c r="CN19" t="inlineStr"/>
+      <c r="CO19" t="inlineStr"/>
+      <c r="CP19" t="inlineStr"/>
+      <c r="CQ19" t="inlineStr"/>
+      <c r="CR19" t="inlineStr"/>
+      <c r="CS19" t="inlineStr"/>
+      <c r="CT19" t="inlineStr"/>
+      <c r="CU19" t="inlineStr"/>
+      <c r="CV19" t="inlineStr"/>
+      <c r="CW19" t="inlineStr"/>
+      <c r="CX19" t="inlineStr"/>
+      <c r="CY19" t="inlineStr"/>
+      <c r="CZ19" t="inlineStr"/>
+      <c r="DA19" t="inlineStr"/>
+      <c r="DB19" t="inlineStr"/>
+      <c r="DC19" t="inlineStr"/>
+      <c r="DD19" t="inlineStr"/>
+      <c r="DE19" t="inlineStr"/>
+      <c r="DF19" t="inlineStr"/>
+      <c r="DG19" t="inlineStr"/>
+      <c r="DH19" t="inlineStr"/>
+      <c r="DI19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3618,6 +4101,27 @@
       <c r="CL20" t="inlineStr"/>
       <c r="CM20" t="inlineStr"/>
       <c r="CN20" t="inlineStr"/>
+      <c r="CO20" t="inlineStr"/>
+      <c r="CP20" t="inlineStr"/>
+      <c r="CQ20" t="inlineStr"/>
+      <c r="CR20" t="inlineStr"/>
+      <c r="CS20" t="inlineStr"/>
+      <c r="CT20" t="inlineStr"/>
+      <c r="CU20" t="inlineStr"/>
+      <c r="CV20" t="inlineStr"/>
+      <c r="CW20" t="inlineStr"/>
+      <c r="CX20" t="inlineStr"/>
+      <c r="CY20" t="inlineStr"/>
+      <c r="CZ20" t="inlineStr"/>
+      <c r="DA20" t="inlineStr"/>
+      <c r="DB20" t="inlineStr"/>
+      <c r="DC20" t="inlineStr"/>
+      <c r="DD20" t="inlineStr"/>
+      <c r="DE20" t="inlineStr"/>
+      <c r="DF20" t="inlineStr"/>
+      <c r="DG20" t="inlineStr"/>
+      <c r="DH20" t="inlineStr"/>
+      <c r="DI20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3788,6 +4292,27 @@
       <c r="CL21" t="inlineStr"/>
       <c r="CM21" t="inlineStr"/>
       <c r="CN21" t="inlineStr"/>
+      <c r="CO21" t="inlineStr"/>
+      <c r="CP21" t="inlineStr"/>
+      <c r="CQ21" t="inlineStr"/>
+      <c r="CR21" t="inlineStr"/>
+      <c r="CS21" t="inlineStr"/>
+      <c r="CT21" t="inlineStr"/>
+      <c r="CU21" t="inlineStr"/>
+      <c r="CV21" t="inlineStr"/>
+      <c r="CW21" t="inlineStr"/>
+      <c r="CX21" t="inlineStr"/>
+      <c r="CY21" t="inlineStr"/>
+      <c r="CZ21" t="inlineStr"/>
+      <c r="DA21" t="inlineStr"/>
+      <c r="DB21" t="inlineStr"/>
+      <c r="DC21" t="inlineStr"/>
+      <c r="DD21" t="inlineStr"/>
+      <c r="DE21" t="inlineStr"/>
+      <c r="DF21" t="inlineStr"/>
+      <c r="DG21" t="inlineStr"/>
+      <c r="DH21" t="inlineStr"/>
+      <c r="DI21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3958,6 +4483,27 @@
       <c r="CL22" t="inlineStr"/>
       <c r="CM22" t="inlineStr"/>
       <c r="CN22" t="inlineStr"/>
+      <c r="CO22" t="inlineStr"/>
+      <c r="CP22" t="inlineStr"/>
+      <c r="CQ22" t="inlineStr"/>
+      <c r="CR22" t="inlineStr"/>
+      <c r="CS22" t="inlineStr"/>
+      <c r="CT22" t="inlineStr"/>
+      <c r="CU22" t="inlineStr"/>
+      <c r="CV22" t="inlineStr"/>
+      <c r="CW22" t="inlineStr"/>
+      <c r="CX22" t="inlineStr"/>
+      <c r="CY22" t="inlineStr"/>
+      <c r="CZ22" t="inlineStr"/>
+      <c r="DA22" t="inlineStr"/>
+      <c r="DB22" t="inlineStr"/>
+      <c r="DC22" t="inlineStr"/>
+      <c r="DD22" t="inlineStr"/>
+      <c r="DE22" t="inlineStr"/>
+      <c r="DF22" t="inlineStr"/>
+      <c r="DG22" t="inlineStr"/>
+      <c r="DH22" t="inlineStr"/>
+      <c r="DI22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4128,6 +4674,27 @@
       <c r="CL23" t="inlineStr"/>
       <c r="CM23" t="inlineStr"/>
       <c r="CN23" t="inlineStr"/>
+      <c r="CO23" t="inlineStr"/>
+      <c r="CP23" t="inlineStr"/>
+      <c r="CQ23" t="inlineStr"/>
+      <c r="CR23" t="inlineStr"/>
+      <c r="CS23" t="inlineStr"/>
+      <c r="CT23" t="inlineStr"/>
+      <c r="CU23" t="inlineStr"/>
+      <c r="CV23" t="inlineStr"/>
+      <c r="CW23" t="inlineStr"/>
+      <c r="CX23" t="inlineStr"/>
+      <c r="CY23" t="inlineStr"/>
+      <c r="CZ23" t="inlineStr"/>
+      <c r="DA23" t="inlineStr"/>
+      <c r="DB23" t="inlineStr"/>
+      <c r="DC23" t="inlineStr"/>
+      <c r="DD23" t="inlineStr"/>
+      <c r="DE23" t="inlineStr"/>
+      <c r="DF23" t="inlineStr"/>
+      <c r="DG23" t="inlineStr"/>
+      <c r="DH23" t="inlineStr"/>
+      <c r="DI23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4380,6 +4947,27 @@
       <c r="CL24" t="inlineStr"/>
       <c r="CM24" t="inlineStr"/>
       <c r="CN24" t="inlineStr"/>
+      <c r="CO24" t="inlineStr"/>
+      <c r="CP24" t="inlineStr"/>
+      <c r="CQ24" t="inlineStr"/>
+      <c r="CR24" t="inlineStr"/>
+      <c r="CS24" t="inlineStr"/>
+      <c r="CT24" t="inlineStr"/>
+      <c r="CU24" t="inlineStr"/>
+      <c r="CV24" t="inlineStr"/>
+      <c r="CW24" t="inlineStr"/>
+      <c r="CX24" t="inlineStr"/>
+      <c r="CY24" t="inlineStr"/>
+      <c r="CZ24" t="inlineStr"/>
+      <c r="DA24" t="inlineStr"/>
+      <c r="DB24" t="inlineStr"/>
+      <c r="DC24" t="inlineStr"/>
+      <c r="DD24" t="inlineStr"/>
+      <c r="DE24" t="inlineStr"/>
+      <c r="DF24" t="inlineStr"/>
+      <c r="DG24" t="inlineStr"/>
+      <c r="DH24" t="inlineStr"/>
+      <c r="DI24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4654,6 +5242,27 @@
       <c r="CL25" t="inlineStr"/>
       <c r="CM25" t="inlineStr"/>
       <c r="CN25" t="inlineStr"/>
+      <c r="CO25" t="inlineStr"/>
+      <c r="CP25" t="inlineStr"/>
+      <c r="CQ25" t="inlineStr"/>
+      <c r="CR25" t="inlineStr"/>
+      <c r="CS25" t="inlineStr"/>
+      <c r="CT25" t="inlineStr"/>
+      <c r="CU25" t="inlineStr"/>
+      <c r="CV25" t="inlineStr"/>
+      <c r="CW25" t="inlineStr"/>
+      <c r="CX25" t="inlineStr"/>
+      <c r="CY25" t="inlineStr"/>
+      <c r="CZ25" t="inlineStr"/>
+      <c r="DA25" t="inlineStr"/>
+      <c r="DB25" t="inlineStr"/>
+      <c r="DC25" t="inlineStr"/>
+      <c r="DD25" t="inlineStr"/>
+      <c r="DE25" t="inlineStr"/>
+      <c r="DF25" t="inlineStr"/>
+      <c r="DG25" t="inlineStr"/>
+      <c r="DH25" t="inlineStr"/>
+      <c r="DI25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4981,6 +5590,431 @@
         <v>0</v>
       </c>
       <c r="CN26" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO26" t="inlineStr"/>
+      <c r="CP26" t="inlineStr"/>
+      <c r="CQ26" t="inlineStr"/>
+      <c r="CR26" t="inlineStr"/>
+      <c r="CS26" t="inlineStr"/>
+      <c r="CT26" t="inlineStr"/>
+      <c r="CU26" t="inlineStr"/>
+      <c r="CV26" t="inlineStr"/>
+      <c r="CW26" t="inlineStr"/>
+      <c r="CX26" t="inlineStr"/>
+      <c r="CY26" t="inlineStr"/>
+      <c r="CZ26" t="inlineStr"/>
+      <c r="DA26" t="inlineStr"/>
+      <c r="DB26" t="inlineStr"/>
+      <c r="DC26" t="inlineStr"/>
+      <c r="DD26" t="inlineStr"/>
+      <c r="DE26" t="inlineStr"/>
+      <c r="DF26" t="inlineStr"/>
+      <c r="DG26" t="inlineStr"/>
+      <c r="DH26" t="inlineStr"/>
+      <c r="DI26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-10-02T14:54:13.419123+00:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.3043469172884722</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.2257540336463174</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0785928836421545</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.7549897760494932</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.1526640167411745</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.09234620720933211</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.7549897760493324</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.1526640167413354</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.0923462072093322</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>FIN_DUAL_PUB_PRIV</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>KD_APR15_MAY15_Klt30_T15</t>
+        </is>
+      </c>
+      <c r="T27" t="b">
+        <v>0</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: COOL_c8_f50_d21 (replace DH, keep FUSE)</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>ACCEPT_2026-09-09_DROP_E45_A05</t>
+        </is>
+      </c>
+      <c r="AG27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>COOL_c8_f50_d21</t>
+        </is>
+      </c>
+      <c r="AI27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0.7549897760494932</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0.1526640167411745</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0.09234620720933211</v>
+      </c>
+      <c r="AM27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>ACCEPT Class D: FinPriv V7 F05</t>
+        </is>
+      </c>
+      <c r="AO27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AQ27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: CONF_RET3_A10_H5 (00631L short-assist under COOL)</t>
+        </is>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>ACCEPT Live Path3 switch emitter: T0_CARVE_FIN_SAT_SWITCH tagged orders (P3_T0_STATE · Soft-Frozen Exact T+1 KEEP elsewhere · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>weight_engine_not_wired</t>
+        </is>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>ledger</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>ACCEPT Path3 weight engine: P3_COMP_SAT_DAILY_POS_LEDGER_A (ledger-scaled recon · Soft 0050 KEEP · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>P3_COMP_SAT_DAILY_POS_LEDGER_A</t>
+        </is>
+      </c>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>ledger_stale</t>
+        </is>
+      </c>
+      <c r="BE27" t="inlineStr"/>
+      <c r="BF27" t="b">
+        <v>1</v>
+      </c>
+      <c r="BG27" t="inlineStr">
+        <is>
+          <t>ACCEPT Soft↔Path3 coexist mute: MUTE_SOFT_FIN_TEL (flip-day Soft FIN/TEL Exact T+1 muted · Soft 0050 KEEP · Path3 -P3T0 KEEP · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>MUTE_SOFT_FIN_TEL</t>
+        </is>
+      </c>
+      <c r="BI27" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK27" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL27" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: T3_COOL_INV_VOL20 (TEL within-sleeve under COOL)</t>
+        </is>
+      </c>
+      <c r="BM27" t="inlineStr">
+        <is>
+          <t>TEL_EQUAL</t>
+        </is>
+      </c>
+      <c r="BN27" t="b">
+        <v>0</v>
+      </c>
+      <c r="BO27" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP27" t="inlineStr">
+        <is>
+          <t>LIVE_TEL_T3_COOL_INV_VOL20</t>
+        </is>
+      </c>
+      <c r="BQ27" t="b">
+        <v>1</v>
+      </c>
+      <c r="BR27" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS27" t="inlineStr">
+        <is>
+          <t>WITHIN_SLEEVE_PATH3</t>
+        </is>
+      </c>
+      <c r="BT27" t="inlineStr">
+        <is>
+          <t>ACCEPT Path3 strategy cutover: WITHIN_SLEEVE_PATH3
+(Soft clips+0050 Exact T+1 KEEP · Soft FIN/TEL Exact T+1 OFF · Path3 ledger daily ·
+ T0_CARVE_FIN_SAT_SWITCH KEEP · broker false · overlays KEEP)</t>
+        </is>
+      </c>
+      <c r="BU27" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV27" t="n">
+        <v>5</v>
+      </c>
+      <c r="BW27" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX27" t="inlineStr">
+        <is>
+          <t>gate_stamps_telemetry</t>
+        </is>
+      </c>
+      <c r="BY27" t="inlineStr">
+        <is>
+          <t>TIPSOFT_P3_LIVE_OVERRIDE_W42_M05_K3</t>
+        </is>
+      </c>
+      <c r="BZ27" t="inlineStr">
+        <is>
+          <t>OVERRIDE_LIVE_W42_M0005_K3</t>
+        </is>
+      </c>
+      <c r="CA27" t="inlineStr">
+        <is>
+          <t>ACCEPT live wire: TIPSOFT_P3_LIVE_OVERRIDE_W42_M05_K3
+(Exact T+1 · 0kb1 MUTE_S3_SAT + force LIVE when lag42 live leads champ by &gt;0.5% for 3d ·
+ Path3 WITHIN_SLEEVE KEEP · Soft FIN/TEL stay OFF · Soft clips+0050 KEEP ·
+ T0_CARVE_FIN_SAT_SWITCH KEEP · Path4 OFF · broker false · dual-paper observe KEEP)</t>
+        </is>
+      </c>
+      <c r="CB27" t="inlineStr">
+        <is>
+          <t>ACCEPT_2026-09-30_TIPSOFT_P3_LIVE_OVERRIDE_W42_M05_K3</t>
+        </is>
+      </c>
+      <c r="CC27" t="inlineStr">
+        <is>
+          <t>Set LIVE.live_tipsoft_live_override=False (live_config.live_tipsoft_live_override); tip Soft Exact T+1 LIVE_OVERRIDE gate stamps off; Path3 WITHIN / Soft FIN/TEL unchanged</t>
+        </is>
+      </c>
+      <c r="CD27" t="inlineStr"/>
+      <c r="CE27" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="CF27" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG27" t="b">
+        <v>1</v>
+      </c>
+      <c r="CH27" t="inlineStr">
+        <is>
+          <t>nav_stale</t>
+        </is>
+      </c>
+      <c r="CI27" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="CJ27" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK27" t="b">
+        <v>1</v>
+      </c>
+      <c r="CL27" t="b">
+        <v>1</v>
+      </c>
+      <c r="CM27" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN27" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO27" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP27" t="inlineStr">
+        <is>
+          <t>path3_gate_ft_cash_apply</t>
+        </is>
+      </c>
+      <c r="CQ27" t="inlineStr">
+        <is>
+          <t>TIPSOFT_P3_TRAIL42_L4_DD_SWITCH</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
+          <t>SW_TRAIL_WHEN_TR_DD_GTE_L4</t>
+        </is>
+      </c>
+      <c r="CS27" t="inlineStr">
+        <is>
+          <t>ACCEPT tip apply: TIPSOFT_P3_TRAIL42_L4_DD_SWITCH
+(tip Soft Exact T+1 · dual-book DD switch · Soft FIN/TEL stay OFF ·
+ Path3 WITHIN KEEP · Path4 OFF · broker false · NOT year-switch · NOT stamps-only)</t>
+        </is>
+      </c>
+      <c r="CT27" t="inlineStr">
+        <is>
+          <t>ACCEPT_2026-10-01_TIPSOFT_P3_TRAIL42_L4_DD_SWITCH</t>
+        </is>
+      </c>
+      <c r="CU27" t="inlineStr">
+        <is>
+          <t>Set LIVE.live_tipsoft_dd_switch=False (live_config.live_tipsoft_dd_switch); tip Soft Exact T+1 DD_SWITCH Path3 gate apply off; Path3 WITHIN / Soft FIN/TEL unchanged</t>
+        </is>
+      </c>
+      <c r="CV27" t="inlineStr"/>
+      <c r="CW27" t="inlineStr"/>
+      <c r="CX27" t="inlineStr"/>
+      <c r="CY27" t="inlineStr"/>
+      <c r="CZ27" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="DA27" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB27" t="b">
+        <v>1</v>
+      </c>
+      <c r="DC27" t="inlineStr">
+        <is>
+          <t>nav_stale</t>
+        </is>
+      </c>
+      <c r="DD27" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="DE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="DF27" t="b">
+        <v>1</v>
+      </c>
+      <c r="DG27" t="b">
+        <v>1</v>
+      </c>
+      <c r="DH27" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI27" t="b">
         <v>0</v>
       </c>
     </row>
@@ -4995,7 +6029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:S27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6471,6 +7505,69 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>538082500.8584005</v>
+      </c>
+      <c r="C27" t="n">
+        <v>17828500.85840048</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.7865165645135342</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0883210286976164</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.0920290102744509</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.09618697344248039</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="b">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>E22_v3_recv_pay_effdelay</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6485,7 +7582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9222,6 +10319,32 @@
       </c>
       <c r="F105" t="n">
         <v>112.9</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-10-02-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>50</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F106" t="n">
+        <v>112.8</v>
       </c>
     </row>
   </sheetData>
@@ -9235,7 +10358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J104"/>
+  <dimension ref="A1:J105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13410,6 +14533,46 @@
         <v>5</v>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-10-01-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>50</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G105" t="n">
+        <v>112.906425</v>
+      </c>
+      <c r="H105" t="n">
+        <v>451625.7</v>
+      </c>
+      <c r="I105" t="n">
+        <v>386.1399735</v>
+      </c>
+      <c r="J105" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DI27"/>
+  <dimension ref="A1:DI28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6018,6 +6018,410 @@
         <v>0</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-10-06T15:23:18.481251+00:00</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.1652834277718758</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.0120470546475116</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.1532363731243645</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.7549897760494932</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.1526640167411745</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.09234620720933211</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.7549897760493324</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.1526640167413354</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.0923462072093322</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>FIN_DUAL_PUB_PRIV</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>KD_APR15_MAY15_Klt30_T15</t>
+        </is>
+      </c>
+      <c r="T28" t="b">
+        <v>0</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: COOL_c8_f50_d21 (replace DH, keep FUSE)</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>ACCEPT_2026-09-09_DROP_E45_A05</t>
+        </is>
+      </c>
+      <c r="AG28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>COOL_c8_f50_d21</t>
+        </is>
+      </c>
+      <c r="AI28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0.7549897760494932</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0.1526640167411745</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0.09234620720933211</v>
+      </c>
+      <c r="AM28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>ACCEPT Class D: FinPriv V7 F05</t>
+        </is>
+      </c>
+      <c r="AO28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AQ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AS28" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: CONF_RET3_A10_H5 (00631L short-assist under COOL)</t>
+        </is>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>ACCEPT Live Path3 switch emitter: T0_CARVE_FIN_SAT_SWITCH tagged orders (P3_T0_STATE · Soft-Frozen Exact T+1 KEEP elsewhere · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>weight_engine_not_wired</t>
+        </is>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="inlineStr">
+        <is>
+          <t>ledger</t>
+        </is>
+      </c>
+      <c r="BB28" t="inlineStr">
+        <is>
+          <t>ACCEPT Path3 weight engine: P3_COMP_SAT_DAILY_POS_LEDGER_A (ledger-scaled recon · Soft 0050 KEEP · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="BC28" t="inlineStr">
+        <is>
+          <t>P3_COMP_SAT_DAILY_POS_LEDGER_A</t>
+        </is>
+      </c>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>ledger_stale</t>
+        </is>
+      </c>
+      <c r="BE28" t="inlineStr"/>
+      <c r="BF28" t="b">
+        <v>1</v>
+      </c>
+      <c r="BG28" t="inlineStr">
+        <is>
+          <t>ACCEPT Soft↔Path3 coexist mute: MUTE_SOFT_FIN_TEL (flip-day Soft FIN/TEL Exact T+1 muted · Soft 0050 KEEP · Path3 -P3T0 KEEP · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>MUTE_SOFT_FIN_TEL</t>
+        </is>
+      </c>
+      <c r="BI28" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK28" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL28" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: T3_COOL_INV_VOL20 (TEL within-sleeve under COOL)</t>
+        </is>
+      </c>
+      <c r="BM28" t="inlineStr">
+        <is>
+          <t>TEL_EQUAL</t>
+        </is>
+      </c>
+      <c r="BN28" t="b">
+        <v>0</v>
+      </c>
+      <c r="BO28" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP28" t="inlineStr">
+        <is>
+          <t>LIVE_TEL_T3_COOL_INV_VOL20</t>
+        </is>
+      </c>
+      <c r="BQ28" t="b">
+        <v>1</v>
+      </c>
+      <c r="BR28" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS28" t="inlineStr">
+        <is>
+          <t>WITHIN_SLEEVE_PATH3</t>
+        </is>
+      </c>
+      <c r="BT28" t="inlineStr">
+        <is>
+          <t>ACCEPT Path3 strategy cutover: WITHIN_SLEEVE_PATH3
+(Soft clips+0050 Exact T+1 KEEP · Soft FIN/TEL Exact T+1 OFF · Path3 ledger daily ·
+ T0_CARVE_FIN_SAT_SWITCH KEEP · broker false · overlays KEEP)</t>
+        </is>
+      </c>
+      <c r="BU28" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV28" t="n">
+        <v>5</v>
+      </c>
+      <c r="BW28" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX28" t="inlineStr">
+        <is>
+          <t>gate_stamps_telemetry</t>
+        </is>
+      </c>
+      <c r="BY28" t="inlineStr">
+        <is>
+          <t>TIPSOFT_P3_LIVE_OVERRIDE_W42_M05_K3</t>
+        </is>
+      </c>
+      <c r="BZ28" t="inlineStr">
+        <is>
+          <t>OVERRIDE_LIVE_W42_M0005_K3</t>
+        </is>
+      </c>
+      <c r="CA28" t="inlineStr">
+        <is>
+          <t>ACCEPT live wire: TIPSOFT_P3_LIVE_OVERRIDE_W42_M05_K3
+(Exact T+1 · 0kb1 MUTE_S3_SAT + force LIVE when lag42 live leads champ by &gt;0.5% for 3d ·
+ Path3 WITHIN_SLEEVE KEEP · Soft FIN/TEL stay OFF · Soft clips+0050 KEEP ·
+ T0_CARVE_FIN_SAT_SWITCH KEEP · Path4 OFF · broker false · dual-paper observe KEEP)</t>
+        </is>
+      </c>
+      <c r="CB28" t="inlineStr">
+        <is>
+          <t>ACCEPT_2026-09-30_TIPSOFT_P3_LIVE_OVERRIDE_W42_M05_K3</t>
+        </is>
+      </c>
+      <c r="CC28" t="inlineStr">
+        <is>
+          <t>Set LIVE.live_tipsoft_live_override=False (live_config.live_tipsoft_live_override); tip Soft Exact T+1 LIVE_OVERRIDE gate stamps off; Path3 WITHIN / Soft FIN/TEL unchanged</t>
+        </is>
+      </c>
+      <c r="CD28" t="inlineStr"/>
+      <c r="CE28" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="CF28" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG28" t="b">
+        <v>1</v>
+      </c>
+      <c r="CH28" t="inlineStr">
+        <is>
+          <t>nav_stale</t>
+        </is>
+      </c>
+      <c r="CI28" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="CJ28" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK28" t="b">
+        <v>1</v>
+      </c>
+      <c r="CL28" t="b">
+        <v>1</v>
+      </c>
+      <c r="CM28" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN28" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO28" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP28" t="inlineStr">
+        <is>
+          <t>path3_gate_ft_cash_apply</t>
+        </is>
+      </c>
+      <c r="CQ28" t="inlineStr">
+        <is>
+          <t>TIPSOFT_P3_TRAIL42_L4_DD_SWITCH</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
+          <t>SW_TRAIL_WHEN_TR_DD_GTE_L4</t>
+        </is>
+      </c>
+      <c r="CS28" t="inlineStr">
+        <is>
+          <t>ACCEPT tip apply: TIPSOFT_P3_TRAIL42_L4_DD_SWITCH
+(tip Soft Exact T+1 · dual-book DD switch · Soft FIN/TEL stay OFF ·
+ Path3 WITHIN KEEP · Path4 OFF · broker false · NOT year-switch · NOT stamps-only)</t>
+        </is>
+      </c>
+      <c r="CT28" t="inlineStr">
+        <is>
+          <t>ACCEPT_2026-10-01_TIPSOFT_P3_TRAIL42_L4_DD_SWITCH</t>
+        </is>
+      </c>
+      <c r="CU28" t="inlineStr">
+        <is>
+          <t>Set LIVE.live_tipsoft_dd_switch=False (live_config.live_tipsoft_dd_switch); tip Soft Exact T+1 DD_SWITCH Path3 gate apply off; Path3 WITHIN / Soft FIN/TEL unchanged</t>
+        </is>
+      </c>
+      <c r="CV28" t="inlineStr"/>
+      <c r="CW28" t="inlineStr"/>
+      <c r="CX28" t="inlineStr"/>
+      <c r="CY28" t="inlineStr"/>
+      <c r="CZ28" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="DA28" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB28" t="b">
+        <v>1</v>
+      </c>
+      <c r="DC28" t="inlineStr">
+        <is>
+          <t>nav_stale</t>
+        </is>
+      </c>
+      <c r="DD28" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="DE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="DF28" t="b">
+        <v>1</v>
+      </c>
+      <c r="DG28" t="b">
+        <v>1</v>
+      </c>
+      <c r="DH28" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI28" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6029,7 +6433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S27"/>
+  <dimension ref="A1:S28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7568,6 +7972,69 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>541062393.2221823</v>
+      </c>
+      <c r="C28" t="n">
+        <v>17712043.22218223</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.7852012176820099</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.08732357042711381</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.09473953585044401</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.0979452165876892</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>E22_v3_recv_pay_effdelay</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7582,7 +8049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10345,6 +10812,32 @@
       </c>
       <c r="F106" t="n">
         <v>112.8</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-10-06-0050-SELL</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>50</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F107" t="n">
+        <v>116.5</v>
       </c>
     </row>
   </sheetData>
@@ -10358,7 +10851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J105"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14573,6 +15066,46 @@
         <v>5</v>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-10-02-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>50</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G106" t="n">
+        <v>116.35815</v>
+      </c>
+      <c r="H106" t="n">
+        <v>116358.15</v>
+      </c>
+      <c r="I106" t="n">
+        <v>99.48621824999999</v>
+      </c>
+      <c r="J106" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DI28"/>
+  <dimension ref="A1:DI29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6422,6 +6422,410 @@
         <v>0</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-10-07T15:43:42.509039+00:00</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.2802399855938747</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.1799904544708676</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.1002495311230072</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.7549897760494932</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.1526640167411745</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.09234620720933211</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.7549897760493324</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.1526640167413354</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.0923462072093322</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>FIN_DUAL_PUB_PRIV</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>KD_APR15_MAY15_Klt30_T15</t>
+        </is>
+      </c>
+      <c r="T29" t="b">
+        <v>0</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: COOL_c8_f50_d21 (replace DH, keep FUSE)</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>ACCEPT_2026-09-09_DROP_E45_A05</t>
+        </is>
+      </c>
+      <c r="AG29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>COOL_c8_f50_d21</t>
+        </is>
+      </c>
+      <c r="AI29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0.7549897760494932</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.1526640167411745</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0.09234620720933211</v>
+      </c>
+      <c r="AM29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>ACCEPT Class D: FinPriv V7 F05</t>
+        </is>
+      </c>
+      <c r="AO29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AQ29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AS29" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: CONF_RET3_A10_H5 (00631L short-assist under COOL)</t>
+        </is>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>ACCEPT Live Path3 switch emitter: T0_CARVE_FIN_SAT_SWITCH tagged orders (P3_T0_STATE · Soft-Frozen Exact T+1 KEEP elsewhere · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>weight_engine_not_wired</t>
+        </is>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>ledger</t>
+        </is>
+      </c>
+      <c r="BB29" t="inlineStr">
+        <is>
+          <t>ACCEPT Path3 weight engine: P3_COMP_SAT_DAILY_POS_LEDGER_A (ledger-scaled recon · Soft 0050 KEEP · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="BC29" t="inlineStr">
+        <is>
+          <t>P3_COMP_SAT_DAILY_POS_LEDGER_A</t>
+        </is>
+      </c>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>ledger_stale</t>
+        </is>
+      </c>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="b">
+        <v>1</v>
+      </c>
+      <c r="BG29" t="inlineStr">
+        <is>
+          <t>ACCEPT Soft↔Path3 coexist mute: MUTE_SOFT_FIN_TEL (flip-day Soft FIN/TEL Exact T+1 muted · Soft 0050 KEEP · Path3 -P3T0 KEEP · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>MUTE_SOFT_FIN_TEL</t>
+        </is>
+      </c>
+      <c r="BI29" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK29" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL29" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: T3_COOL_INV_VOL20 (TEL within-sleeve under COOL)</t>
+        </is>
+      </c>
+      <c r="BM29" t="inlineStr">
+        <is>
+          <t>TEL_EQUAL</t>
+        </is>
+      </c>
+      <c r="BN29" t="b">
+        <v>0</v>
+      </c>
+      <c r="BO29" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP29" t="inlineStr">
+        <is>
+          <t>LIVE_TEL_T3_COOL_INV_VOL20</t>
+        </is>
+      </c>
+      <c r="BQ29" t="b">
+        <v>1</v>
+      </c>
+      <c r="BR29" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS29" t="inlineStr">
+        <is>
+          <t>WITHIN_SLEEVE_PATH3</t>
+        </is>
+      </c>
+      <c r="BT29" t="inlineStr">
+        <is>
+          <t>ACCEPT Path3 strategy cutover: WITHIN_SLEEVE_PATH3
+(Soft clips+0050 Exact T+1 KEEP · Soft FIN/TEL Exact T+1 OFF · Path3 ledger daily ·
+ T0_CARVE_FIN_SAT_SWITCH KEEP · broker false · overlays KEEP)</t>
+        </is>
+      </c>
+      <c r="BU29" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV29" t="n">
+        <v>5</v>
+      </c>
+      <c r="BW29" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX29" t="inlineStr">
+        <is>
+          <t>gate_stamps_telemetry</t>
+        </is>
+      </c>
+      <c r="BY29" t="inlineStr">
+        <is>
+          <t>TIPSOFT_P3_LIVE_OVERRIDE_W42_M05_K3</t>
+        </is>
+      </c>
+      <c r="BZ29" t="inlineStr">
+        <is>
+          <t>OVERRIDE_LIVE_W42_M0005_K3</t>
+        </is>
+      </c>
+      <c r="CA29" t="inlineStr">
+        <is>
+          <t>ACCEPT live wire: TIPSOFT_P3_LIVE_OVERRIDE_W42_M05_K3
+(Exact T+1 · 0kb1 MUTE_S3_SAT + force LIVE when lag42 live leads champ by &gt;0.5% for 3d ·
+ Path3 WITHIN_SLEEVE KEEP · Soft FIN/TEL stay OFF · Soft clips+0050 KEEP ·
+ T0_CARVE_FIN_SAT_SWITCH KEEP · Path4 OFF · broker false · dual-paper observe KEEP)</t>
+        </is>
+      </c>
+      <c r="CB29" t="inlineStr">
+        <is>
+          <t>ACCEPT_2026-09-30_TIPSOFT_P3_LIVE_OVERRIDE_W42_M05_K3</t>
+        </is>
+      </c>
+      <c r="CC29" t="inlineStr">
+        <is>
+          <t>Set LIVE.live_tipsoft_live_override=False (live_config.live_tipsoft_live_override); tip Soft Exact T+1 LIVE_OVERRIDE gate stamps off; Path3 WITHIN / Soft FIN/TEL unchanged</t>
+        </is>
+      </c>
+      <c r="CD29" t="inlineStr"/>
+      <c r="CE29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="CF29" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG29" t="b">
+        <v>1</v>
+      </c>
+      <c r="CH29" t="inlineStr">
+        <is>
+          <t>nav_stale</t>
+        </is>
+      </c>
+      <c r="CI29" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="CJ29" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK29" t="b">
+        <v>1</v>
+      </c>
+      <c r="CL29" t="b">
+        <v>1</v>
+      </c>
+      <c r="CM29" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN29" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO29" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP29" t="inlineStr">
+        <is>
+          <t>path3_gate_ft_cash_apply</t>
+        </is>
+      </c>
+      <c r="CQ29" t="inlineStr">
+        <is>
+          <t>TIPSOFT_P3_TRAIL42_L4_DD_SWITCH</t>
+        </is>
+      </c>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>SW_TRAIL_WHEN_TR_DD_GTE_L4</t>
+        </is>
+      </c>
+      <c r="CS29" t="inlineStr">
+        <is>
+          <t>ACCEPT tip apply: TIPSOFT_P3_TRAIL42_L4_DD_SWITCH
+(tip Soft Exact T+1 · dual-book DD switch · Soft FIN/TEL stay OFF ·
+ Path3 WITHIN KEEP · Path4 OFF · broker false · NOT year-switch · NOT stamps-only)</t>
+        </is>
+      </c>
+      <c r="CT29" t="inlineStr">
+        <is>
+          <t>ACCEPT_2026-10-01_TIPSOFT_P3_TRAIL42_L4_DD_SWITCH</t>
+        </is>
+      </c>
+      <c r="CU29" t="inlineStr">
+        <is>
+          <t>Set LIVE.live_tipsoft_dd_switch=False (live_config.live_tipsoft_dd_switch); tip Soft Exact T+1 DD_SWITCH Path3 gate apply off; Path3 WITHIN / Soft FIN/TEL unchanged</t>
+        </is>
+      </c>
+      <c r="CV29" t="inlineStr"/>
+      <c r="CW29" t="inlineStr"/>
+      <c r="CX29" t="inlineStr"/>
+      <c r="CY29" t="inlineStr"/>
+      <c r="CZ29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="DA29" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB29" t="b">
+        <v>1</v>
+      </c>
+      <c r="DC29" t="inlineStr">
+        <is>
+          <t>nav_stale</t>
+        </is>
+      </c>
+      <c r="DD29" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="DE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="DF29" t="b">
+        <v>1</v>
+      </c>
+      <c r="DG29" t="b">
+        <v>1</v>
+      </c>
+      <c r="DH29" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI29" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6433,7 +6837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S28"/>
+  <dimension ref="A1:S29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8035,6 +8439,69 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>549061405.8180152</v>
+      </c>
+      <c r="C29" t="n">
+        <v>18639055.81801524</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.7881782354657731</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.08656682020690749</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.0913078199792768</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.1003240431806023</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="b">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>E22_v3_recv_pay_effdelay</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8049,7 +8516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10838,6 +11305,32 @@
       </c>
       <c r="F107" t="n">
         <v>116.5</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-10-07-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>50</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F108" t="n">
+        <v>116.05</v>
       </c>
     </row>
   </sheetData>
@@ -10851,7 +11344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J106"/>
+  <dimension ref="A1:J107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15106,6 +15599,46 @@
         <v>5</v>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-10-06-0050-SELL</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>50</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G107" t="n">
+        <v>116.091925</v>
+      </c>
+      <c r="H107" t="n">
+        <v>928735.4</v>
+      </c>
+      <c r="I107" t="n">
+        <v>1722.804167</v>
+      </c>
+      <c r="J107" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/forward/e21/E21_forward_dashboard.xlsx
+++ b/forward/e21/E21_forward_dashboard.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DI29"/>
+  <dimension ref="A1:DI30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6826,6 +6826,410 @@
         <v>0</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-10-08T15:48:11.953125+00:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bull</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>-0.2814441324930231</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.345955443425105</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-0.06451131093208171</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.7549897760494932</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.1526640167411745</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.09234620720933211</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.7549897760493324</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.1526640167413354</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.0923462072093322</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>FIN_DUAL_PUB_PRIV</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>KD_APR15_MAY15_Klt30_T15</t>
+        </is>
+      </c>
+      <c r="T30" t="b">
+        <v>0</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: COOL_c8_f50_d21 (replace DH, keep FUSE)</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>ACCEPT_2026-09-09_DROP_E45_A05</t>
+        </is>
+      </c>
+      <c r="AG30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>COOL_c8_f50_d21</t>
+        </is>
+      </c>
+      <c r="AI30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0.7549897760494932</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0.1526640167411745</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0.09234620720933211</v>
+      </c>
+      <c r="AM30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>ACCEPT Class D: FinPriv V7 F05</t>
+        </is>
+      </c>
+      <c r="AO30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AQ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: CONF_RET3_A10_H5 (00631L short-assist under COOL)</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>ACCEPT Live Path3 switch emitter: T0_CARVE_FIN_SAT_SWITCH tagged orders (P3_T0_STATE · Soft-Frozen Exact T+1 KEEP elsewhere · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>weight_engine_not_wired</t>
+        </is>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="inlineStr">
+        <is>
+          <t>ledger</t>
+        </is>
+      </c>
+      <c r="BB30" t="inlineStr">
+        <is>
+          <t>ACCEPT Path3 weight engine: P3_COMP_SAT_DAILY_POS_LEDGER_A (ledger-scaled recon · Soft 0050 KEEP · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="BC30" t="inlineStr">
+        <is>
+          <t>P3_COMP_SAT_DAILY_POS_LEDGER_A</t>
+        </is>
+      </c>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>ledger_stale</t>
+        </is>
+      </c>
+      <c r="BE30" t="inlineStr"/>
+      <c r="BF30" t="b">
+        <v>1</v>
+      </c>
+      <c r="BG30" t="inlineStr">
+        <is>
+          <t>ACCEPT Soft↔Path3 coexist mute: MUTE_SOFT_FIN_TEL (flip-day Soft FIN/TEL Exact T+1 muted · Soft 0050 KEEP · Path3 -P3T0 KEEP · cutover still BLOCKED)</t>
+        </is>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>MUTE_SOFT_FIN_TEL</t>
+        </is>
+      </c>
+      <c r="BI30" t="b">
+        <v>0</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK30" t="b">
+        <v>1</v>
+      </c>
+      <c r="BL30" t="inlineStr">
+        <is>
+          <t>ACCEPT Live cutover: T3_COOL_INV_VOL20 (TEL within-sleeve under COOL)</t>
+        </is>
+      </c>
+      <c r="BM30" t="inlineStr">
+        <is>
+          <t>TEL_EQUAL</t>
+        </is>
+      </c>
+      <c r="BN30" t="b">
+        <v>0</v>
+      </c>
+      <c r="BO30" t="b">
+        <v>0</v>
+      </c>
+      <c r="BP30" t="inlineStr">
+        <is>
+          <t>LIVE_TEL_T3_COOL_INV_VOL20</t>
+        </is>
+      </c>
+      <c r="BQ30" t="b">
+        <v>1</v>
+      </c>
+      <c r="BR30" t="b">
+        <v>1</v>
+      </c>
+      <c r="BS30" t="inlineStr">
+        <is>
+          <t>WITHIN_SLEEVE_PATH3</t>
+        </is>
+      </c>
+      <c r="BT30" t="inlineStr">
+        <is>
+          <t>ACCEPT Path3 strategy cutover: WITHIN_SLEEVE_PATH3
+(Soft clips+0050 Exact T+1 KEEP · Soft FIN/TEL Exact T+1 OFF · Path3 ledger daily ·
+ T0_CARVE_FIN_SAT_SWITCH KEEP · broker false · overlays KEEP)</t>
+        </is>
+      </c>
+      <c r="BU30" t="b">
+        <v>1</v>
+      </c>
+      <c r="BV30" t="n">
+        <v>5</v>
+      </c>
+      <c r="BW30" t="b">
+        <v>1</v>
+      </c>
+      <c r="BX30" t="inlineStr">
+        <is>
+          <t>gate_stamps_telemetry</t>
+        </is>
+      </c>
+      <c r="BY30" t="inlineStr">
+        <is>
+          <t>TIPSOFT_P3_LIVE_OVERRIDE_W42_M05_K3</t>
+        </is>
+      </c>
+      <c r="BZ30" t="inlineStr">
+        <is>
+          <t>OVERRIDE_LIVE_W42_M0005_K3</t>
+        </is>
+      </c>
+      <c r="CA30" t="inlineStr">
+        <is>
+          <t>ACCEPT live wire: TIPSOFT_P3_LIVE_OVERRIDE_W42_M05_K3
+(Exact T+1 · 0kb1 MUTE_S3_SAT + force LIVE when lag42 live leads champ by &gt;0.5% for 3d ·
+ Path3 WITHIN_SLEEVE KEEP · Soft FIN/TEL stay OFF · Soft clips+0050 KEEP ·
+ T0_CARVE_FIN_SAT_SWITCH KEEP · Path4 OFF · broker false · dual-paper observe KEEP)</t>
+        </is>
+      </c>
+      <c r="CB30" t="inlineStr">
+        <is>
+          <t>ACCEPT_2026-09-30_TIPSOFT_P3_LIVE_OVERRIDE_W42_M05_K3</t>
+        </is>
+      </c>
+      <c r="CC30" t="inlineStr">
+        <is>
+          <t>Set LIVE.live_tipsoft_live_override=False (live_config.live_tipsoft_live_override); tip Soft Exact T+1 LIVE_OVERRIDE gate stamps off; Path3 WITHIN / Soft FIN/TEL unchanged</t>
+        </is>
+      </c>
+      <c r="CD30" t="inlineStr"/>
+      <c r="CE30" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="CF30" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG30" t="b">
+        <v>1</v>
+      </c>
+      <c r="CH30" t="inlineStr">
+        <is>
+          <t>nav_stale</t>
+        </is>
+      </c>
+      <c r="CI30" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="CJ30" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK30" t="b">
+        <v>1</v>
+      </c>
+      <c r="CL30" t="b">
+        <v>1</v>
+      </c>
+      <c r="CM30" t="b">
+        <v>0</v>
+      </c>
+      <c r="CN30" t="b">
+        <v>0</v>
+      </c>
+      <c r="CO30" t="b">
+        <v>1</v>
+      </c>
+      <c r="CP30" t="inlineStr">
+        <is>
+          <t>path3_gate_ft_cash_apply</t>
+        </is>
+      </c>
+      <c r="CQ30" t="inlineStr">
+        <is>
+          <t>TIPSOFT_P3_TRAIL42_L4_DD_SWITCH</t>
+        </is>
+      </c>
+      <c r="CR30" t="inlineStr">
+        <is>
+          <t>SW_TRAIL_WHEN_TR_DD_GTE_L4</t>
+        </is>
+      </c>
+      <c r="CS30" t="inlineStr">
+        <is>
+          <t>ACCEPT tip apply: TIPSOFT_P3_TRAIL42_L4_DD_SWITCH
+(tip Soft Exact T+1 · dual-book DD switch · Soft FIN/TEL stay OFF ·
+ Path3 WITHIN KEEP · Path4 OFF · broker false · NOT year-switch · NOT stamps-only)</t>
+        </is>
+      </c>
+      <c r="CT30" t="inlineStr">
+        <is>
+          <t>ACCEPT_2026-10-01_TIPSOFT_P3_TRAIL42_L4_DD_SWITCH</t>
+        </is>
+      </c>
+      <c r="CU30" t="inlineStr">
+        <is>
+          <t>Set LIVE.live_tipsoft_dd_switch=False (live_config.live_tipsoft_dd_switch); tip Soft Exact T+1 DD_SWITCH Path3 gate apply off; Path3 WITHIN / Soft FIN/TEL unchanged</t>
+        </is>
+      </c>
+      <c r="CV30" t="inlineStr"/>
+      <c r="CW30" t="inlineStr"/>
+      <c r="CX30" t="inlineStr"/>
+      <c r="CY30" t="inlineStr"/>
+      <c r="CZ30" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="DA30" t="b">
+        <v>0</v>
+      </c>
+      <c r="DB30" t="b">
+        <v>1</v>
+      </c>
+      <c r="DC30" t="inlineStr">
+        <is>
+          <t>nav_stale</t>
+        </is>
+      </c>
+      <c r="DD30" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="DE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="DF30" t="b">
+        <v>1</v>
+      </c>
+      <c r="DG30" t="b">
+        <v>1</v>
+      </c>
+      <c r="DH30" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI30" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6837,7 +7241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S29"/>
+  <dimension ref="A1:S30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8502,6 +8906,69 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>543972686.7723289</v>
+      </c>
+      <c r="C30" t="n">
+        <v>18292536.77232886</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.7866514448345783</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0877985258476574</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.09192235422093541</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.09695101266699881</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>E22_v3_recv_pay_effdelay</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8516,7 +8983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11331,6 +11798,32 @@
       </c>
       <c r="F108" t="n">
         <v>116.05</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-10-08-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>50</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F109" t="n">
+        <v>114.95</v>
       </c>
     </row>
   </sheetData>
@@ -11344,7 +11837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15639,6 +16132,46 @@
         <v>5</v>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-10-07-0050-BUY</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>50</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G108" t="n">
+        <v>115.407675</v>
+      </c>
+      <c r="H108" t="n">
+        <v>346223.025</v>
+      </c>
+      <c r="I108" t="n">
+        <v>296.020686375</v>
+      </c>
+      <c r="J108" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
